--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_gy(s1).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_gy(s1).xlsx
@@ -12,7 +12,7 @@
     <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
-    <sheet name="圣诺汀之梦_盖亚之心（索菲亚线上）" sheetId="1" r:id="rId1"/>
+    <sheet name="圣诺汀之梦_盖亚之心（索菲亚线上） (1)" sheetId="1" r:id="rId1"/>
     <sheet name="转换说明" sheetId="2" r:id="rId2"/>
     <sheet name="命令库" sheetId="3" r:id="rId3"/>
   </sheets>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1330" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1378" uniqueCount="491">
   <si>
     <t>ID</t>
   </si>
@@ -180,13 +180,19 @@
     <t>源类型=type:txt_Gaiman; 层级=9</t>
   </si>
   <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>源类型=type:exeBC; 层级=10</t>
+  </si>
+  <si>
     <t>13</t>
   </si>
   <si>
     <t>他的目光在大卫身上微微沾粘了一瞬，随后识趣地移回到你们身上。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=10</t>
+    <t>源类型=type:txt_pb; 层级=11</t>
   </si>
   <si>
     <t>14</t>
@@ -195,7 +201,7 @@
     <t>所以我把数据藏在了这里，等着合适的人来。既然索菲亚带你们来了，我想——你们应该就是我一直等的人。</t>
   </si>
   <si>
-    <t>源类型=type:txt_Gaiman; 层级=11</t>
+    <t>源类型=type:txt_Gaiman; 层级=12</t>
   </si>
   <si>
     <t>15</t>
@@ -207,7 +213,7 @@
     <t>charfadeout(L,1)</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=12</t>
+    <t>源类型=type:txt_pb; 层级=13</t>
   </si>
   <si>
     <t>16</t>
@@ -222,7 +228,7 @@
     <t>你就这么相信我们？</t>
   </si>
   <si>
-    <t>源类型=type:txt_Clark; 层级=13</t>
+    <t>源类型=type:txt_Clark; 层级=14</t>
   </si>
   <si>
     <t>17</t>
@@ -231,7 +237,7 @@
     <t>克拉克仍举着枪，但手指没有扣在扳机上，只是象征性地维持着戒备的姿态，让对方知道他们这三头困兽依然保留着用于撕咬的利齿，不是任他利用的工具。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=14</t>
+    <t>源类型=type:txt_pb; 层级=15</t>
   </si>
   <si>
     <t>18</t>
@@ -240,7 +246,7 @@
     <t>自从你们踏入这个梦境的那一刻，我就一直在观察着你们的一举一动。而且......如果不是她最终给予了你们同等的信任，我想你们也大概找不到这里。</t>
   </si>
   <si>
-    <t>源类型=type:txt_Gaiman; 层级=15</t>
+    <t>源类型=type:txt_Gaiman; 层级=16</t>
   </si>
   <si>
     <t>19</t>
@@ -249,7 +255,7 @@
     <t>他肩上的飞蛾在这句话落下的刹那再次振翅而起，围着你们三个人转了一大圈。每当你们面临关键的抉择，或在某个岔路口迷路时，这只体积不足方寸的生物就会及时出现在你们面前，帮你们指明前进的方向。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=16</t>
+    <t>源类型=type:txt_pb; 层级=17</t>
   </si>
   <si>
     <t>20</t>
@@ -258,7 +264,7 @@
     <t>看来从一开始，它就在亚波伦控制的大片区域中静悄悄地充当着盖曼的耳目。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=17</t>
+    <t>源类型=type:txt_pb; 层级=18</t>
   </si>
   <si>
     <t>21</t>
@@ -267,7 +273,7 @@
     <t>索菲亚终于凑近过来，她的声音从你身后传出，带着一种欣慰之余又混杂着一丝难言的苦涩。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=18</t>
+    <t>源类型=type:txt_pb; 层级=19</t>
   </si>
   <si>
     <t>22</t>
@@ -282,7 +288,7 @@
     <t>……你还真是一点也没变，无论外貌还是做事的方式。</t>
   </si>
   <si>
-    <t>源类型=type:txt_Sophia; 层级=19</t>
+    <t>源类型=type:txt_Sophia; 层级=20</t>
   </si>
   <si>
     <t>23</t>
@@ -291,7 +297,7 @@
     <t>盖曼微微侧身看向她，嘴角浮起一个几乎看不出弧度的微笑。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=20</t>
+    <t>源类型=type:txt_pb; 层级=21</t>
   </si>
   <si>
     <t>24</t>
@@ -300,7 +306,7 @@
     <t>……因为变了的部分都被分到亚波伦那边了。</t>
   </si>
   <si>
-    <t>源类型=type:txt_Gaiman; 层级=21</t>
+    <t>源类型=type:txt_Gaiman; 层级=22</t>
   </si>
   <si>
     <t>25</t>
@@ -309,7 +315,7 @@
     <t>索菲亚低下头，发丝垂下来挡住半张脸，将她这些年的脆弱和委屈揉成了一团模糊的阴影。那些攒了快半辈子的情绪在这一刻终于找到了可以释放的出口。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=22</t>
+    <t>源类型=type:txt_pb; 层级=23</t>
   </si>
   <si>
     <t>26</t>
@@ -318,7 +324,7 @@
     <t>可我变了。你走了之后……我在公司那边做了很多事情。我被骗过，也明知有些事不对还做了。我劝那些病人躺进造梦设备里，我知道他们在梦里要经历什么，但我还是.....</t>
   </si>
   <si>
-    <t>源类型=type:txt_Sophia; 层级=23</t>
+    <t>源类型=type:txt_Sophia; 层级=24</t>
   </si>
   <si>
     <t>27</t>
@@ -327,7 +333,7 @@
     <t>她说到这里停住了，像是一句话走到悬崖边上，不知道该不该继续向前。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=24</t>
+    <t>源类型=type:txt_pb; 层级=25</t>
   </si>
   <si>
     <t>28</t>
@@ -336,7 +342,7 @@
     <t>在力量不够的时候，任谁都会有妥协。</t>
   </si>
   <si>
-    <t>源类型=type:txt_Gaiman; 层级=25</t>
+    <t>源类型=type:txt_Gaiman; 层级=26</t>
   </si>
   <si>
     <t>29</t>
@@ -345,7 +351,7 @@
     <t>他的目光落在自己悬在身侧的一只手掌上，那手掌的轮廓在灯光中微微透明，仿佛正缓慢地散成无数细碎的光絮。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=26</t>
+    <t>源类型=type:txt_pb; 层级=27</t>
   </si>
   <si>
     <t>30</t>
@@ -354,7 +360,7 @@
     <t>我被困在这里的时候，看着亚波伦用那些病人在梦里一遍又一遍训练，无限循环地死亡，直到他们被折磨成没有意识的活体兵器。我知道那些事在外面发生，却阻止不了他。</t>
   </si>
   <si>
-    <t>源类型=type:txt_Gaiman; 层级=27</t>
+    <t>源类型=type:txt_Gaiman; 层级=28</t>
   </si>
   <si>
     <t>31</t>
@@ -363,7 +369,7 @@
     <t>他抬眼看向索菲亚，眼神柔和得像那片能在悬崖底部兜住她的云朵：</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=28</t>
+    <t>源类型=type:txt_pb; 层级=29</t>
   </si>
   <si>
     <t>32</t>
@@ -372,7 +378,7 @@
     <t>所以——从某种角度来说，我们也算是同罪。</t>
   </si>
   <si>
-    <t>源类型=type:txt_Gaiman; 层级=29</t>
+    <t>源类型=type:txt_Gaiman; 层级=30</t>
   </si>
   <si>
     <t>33</t>
@@ -381,13 +387,13 @@
     <t>当话题触及“罪孽”二字时，大卫平放于腰侧的手指紧紧攥成了拳头。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=30</t>
+    <t>源类型=type:txt_pb; 层级=31</t>
   </si>
   <si>
     <t>34</t>
   </si>
   <si>
-    <t>源类型=type:exeBC; 层级=31</t>
+    <t>源类型=type:exeBC; 层级=32</t>
   </si>
   <si>
     <t>35</t>
@@ -396,7 +402,7 @@
     <t>和从始至终都知道自己在做些什么的索菲亚不同，当他在电刑椅上被亚波伦细数那些自己曾经犯下的过错——那些为了名利所进行的不实宣传，为了高额酬金而撒下的谎言。以及因为这些谎言而被毁掉整个人生的阿兰.斯科特。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=32; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"端详飞蛾（克拉克）","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}</t>
+    <t>源类型=type:txt_pb; 层级=33; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"端详飞蛾（克拉克）","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}</t>
   </si>
   <si>
     <t>37</t>
@@ -405,7 +411,7 @@
     <t>浮现于脑海中的却只剩下被纳丁达克洗去记忆后的，迷迷糊糊的负罪感。他不知道那些罪行是何时发生的、不知道犯下罪行的自己是否还有资格成为身旁两人的同伴、更不知道赎罪二字对于自己而言，是否已经太迟。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=33</t>
+    <t>源类型=type:txt_pb; 层级=34</t>
   </si>
   <si>
     <t>38</t>
@@ -414,7 +420,7 @@
     <t>只有那盘记录着那场听证会的，正面写着一个大大的“L”的磁带，始终安安稳稳躺在他口袋里，时刻提醒着自己身为骗子（Liar）的过去。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=34</t>
+    <t>源类型=type:txt_pb; 层级=35</t>
   </si>
   <si>
     <t>41</t>
@@ -423,7 +429,7 @@
     <t>但你后来对设备动了手脚。你给了他们看到真相的机会，也给了自己一个重新选择的机会。你选择了为做过的事负责，哪怕那负责的方式是一条很长的路。</t>
   </si>
   <si>
-    <t>源类型=type:txt_Gaiman; 层级=35</t>
+    <t>源类型=type:txt_Gaiman; 层级=36</t>
   </si>
   <si>
     <t>42</t>
@@ -432,7 +438,7 @@
     <t>盖曼语气中的柔和一如往昔，带着跨越时间的温度，一点点地融化了那些在寒夜独行中结出的坚冰。即使一切早已物是人非，即使身处如此绝望的境地，他依旧是她的老师，从未变过。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=36</t>
+    <t>源类型=type:txt_pb; 层级=37</t>
   </si>
   <si>
     <t>43</t>
@@ -441,7 +447,7 @@
     <t>所以，我想这份选择的背后并非只有罪孽，索菲亚。在力量还不足以改变一切的时候，隐忍和积累往往比以卵击石更有可能改变现状。</t>
   </si>
   <si>
-    <t>源类型=type:txt_Gaiman; 层级=37</t>
+    <t>源类型=type:txt_Gaiman; 层级=38</t>
   </si>
   <si>
     <t>44</t>
@@ -450,7 +456,7 @@
     <t>房间里安静了一会儿。培养罐里的心脏还在缓慢跳动，发出低频的、几乎被听觉忽略的震动声。索菲亚站在容器下方的阴影里，发梢被她自己攥得有些蜷曲。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=38</t>
+    <t>源类型=type:txt_pb; 层级=39</t>
   </si>
   <si>
     <t>45</t>
@@ -459,7 +465,7 @@
     <t>你没有看她，却能听见她压在喉咙里的细微抽气声，像一片被雨打湿的羽毛，轻轻蹭在所有人的心口。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=39</t>
+    <t>源类型=type:txt_pb; 层级=40</t>
   </si>
   <si>
     <t>46</t>
@@ -474,7 +480,7 @@
     <t>那现在要怎么做？我们都已经走到这一步了，这一切必须得有个结果，不是吗？</t>
   </si>
   <si>
-    <t>源类型=type:txt_David; 层级=40</t>
+    <t>源类型=type:txt_David; 层级=41</t>
   </si>
   <si>
     <t>47</t>
@@ -483,7 +489,7 @@
     <t>一丝焦急混着久积的沉郁从他话音浅浅地里溢出来，像一个于时无多的病人，试图在最后时刻再完成些什么，或者说......尝试挽回些什么。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=41</t>
+    <t>源类型=type:txt_pb; 层级=42</t>
   </si>
   <si>
     <t>48</t>
@@ -492,7 +498,7 @@
     <t>盖曼缓缓点了点头，抬起手按在自己的左胸位置，那只停在窗边的飞蛾又一次振翅扑棱着翅膀落回了他的手背，翅膀上那层细腻的灰白色鳞粉在灯光下泛着细碎的光。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=42</t>
+    <t>源类型=type:txt_pb; 层级=43</t>
   </si>
   <si>
     <t>49</t>
@@ -504,7 +510,7 @@
     <t>bgfade(sntzm_gy(s1)_49,1)</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=43</t>
+    <t>源类型=type:txt_pb; 层级=44</t>
   </si>
   <si>
     <t>50</t>
@@ -513,7 +519,7 @@
     <t>纳丁达克总是把一切都当做增长利润的工具看待，正如培养罐里跳动的那颗机械心脏。完美符合了他们对“盖亚之心”的外形想象。</t>
   </si>
   <si>
-    <t>源类型=type:txt_Gaiman; 层级=44</t>
+    <t>源类型=type:txt_Gaiman; 层级=45</t>
   </si>
   <si>
     <t>51</t>
@@ -522,7 +528,7 @@
     <t>但他们忘了，无论是造梦设备，还是他们所谓的“盖亚之心”。最初都是为了拯救生命而被创造，所以它在梦境中的表现形式也必然只会是生命。</t>
   </si>
   <si>
-    <t>源类型=type:txt_Gaiman; 层级=45</t>
+    <t>源类型=type:txt_Gaiman; 层级=46</t>
   </si>
   <si>
     <t>52</t>
@@ -534,13 +540,13 @@
     <t>！？</t>
   </si>
   <si>
-    <t>源类型=type:txt_You; 层级=46</t>
+    <t>源类型=type:txt_You; 层级=47</t>
   </si>
   <si>
     <t>53</t>
   </si>
   <si>
-    <t>源类型=type:txt_Clark; 层级=47</t>
+    <t>源类型=type:txt_Clark; 层级=48</t>
   </si>
   <si>
     <t>54</t>
@@ -549,7 +555,7 @@
     <t>你的意思是说......我们最初苦苦寻找的盖亚之心，其实一直都在我们眼皮子底下飞来飞去？</t>
   </si>
   <si>
-    <t>源类型=type:txt_David; 层级=48</t>
+    <t>源类型=type:txt_David; 层级=49</t>
   </si>
   <si>
     <t>55</t>
@@ -561,7 +567,7 @@
     <t>bgfade(sntzm_gy(2)_66,1)</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=49</t>
+    <t>源类型=type:txt_pb; 层级=50</t>
   </si>
   <si>
     <t>56</t>
@@ -570,7 +576,7 @@
     <t>不止是它的生命，也是我的。只是在亚波伦掌控的那片领域中，我只能以这种低调的方式默默为你们提供帮助。</t>
   </si>
   <si>
-    <t>源类型=type:txt_Gaiman; 层级=50</t>
+    <t>源类型=type:txt_Gaiman; 层级=51</t>
   </si>
   <si>
     <t>57</t>
@@ -579,7 +585,7 @@
     <t>话音刚落，一幅交织着零星线索的画面便在你脑海中徐徐铺开，在三层盖曼的办公室外，当你们被这只飞蛾指引着来到门口时，它曾短暂地停在了办公室门牌的“盖曼”二字上。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=51</t>
+    <t>源类型=type:txt_pb; 层级=52</t>
   </si>
   <si>
     <t>58</t>
@@ -588,13 +594,13 @@
     <t>原来早在那时候这只由盖曼伪装而成的生物就已经向你们发出暗示——不是“盖曼在这里”，而是“我就是盖曼”。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=52</t>
+    <t>源类型=type:txt_pb; 层级=53</t>
   </si>
   <si>
     <t>59</t>
   </si>
   <si>
-    <t>源类型=type:exeBC; 层级=53</t>
+    <t>源类型=type:exeBC; 层级=54</t>
   </si>
   <si>
     <t>60</t>
@@ -603,7 +609,7 @@
     <t>克拉克的枪口不自觉地放了下来，他看着那只安安静静停在手背的灰白色飞蛾，眉头渐渐舒展，他回想起在B2-15号病房，当自己扑向门外那颗弹壳时的场景——</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=54; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"克拉克线","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}</t>
+    <t>源类型=type:txt_pb; 层级=55; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"克拉克线","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}</t>
   </si>
   <si>
     <t>62</t>
@@ -615,7 +621,7 @@
     <t>jump(64)</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=55; gotomainline=64</t>
+    <t>源类型=type:txt_pb; 层级=56; gotomainline=64</t>
   </si>
   <si>
     <t>61</t>
@@ -624,7 +630,7 @@
     <t>克拉克的枪口不自觉地放了下来，他看着那只安安静静停在手背的灰白色飞蛾，眉头渐渐舒展。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=54; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"无视飞蛾（大卫）","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}</t>
+    <t>源类型=type:txt_pb; 层级=55; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"无视飞蛾（大卫）","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}</t>
   </si>
   <si>
     <t>63</t>
@@ -633,7 +639,7 @@
     <t>所有过去捋不清的疑惑此刻突然有了清晰的答案：每一次迷路时的引路、每一次遭遇危险前的预警，甚至每一次帮你们避开亚波伦布下的陷阱，全都出自眼前这只不起眼的飞蛾之手。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=55</t>
+    <t>源类型=type:txt_pb; 层级=56</t>
   </si>
   <si>
     <t>64</t>
@@ -642,7 +648,13 @@
     <t>大卫一直站在角落里，背靠着墙壁，双手交叉抱在胸前。把身体的重量交给墙壁，好让自己不需要为站姿分出额外的注意力。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=56</t>
+    <t>源类型=type:txt_pb; 层级=57</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>源类型=type:exeBC; 层级=58</t>
   </si>
   <si>
     <t>65</t>
@@ -651,7 +663,7 @@
     <t>他的目光在盖曼与那只灰白飞蛾间游移了片刻，最后定格于自己的右肩——那里晕着一块炭灰般的深色粉末，在他离开手术室后那段模糊的记忆中，他隐约觉得这里曾被某样东西附着过。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=57</t>
+    <t>源类型=type:txt_pb; 层级=59</t>
   </si>
   <si>
     <t>66</t>
@@ -660,7 +672,7 @@
     <t>因此，我有一件事，需要你们帮我完成。</t>
   </si>
   <si>
-    <t>源类型=type:txt_Gaiman; 层级=58</t>
+    <t>源类型=type:txt_Gaiman; 层级=60</t>
   </si>
   <si>
     <t>67</t>
@@ -669,7 +681,7 @@
     <t>盖曼抬手指向自己胸口的位置，那只飞蛾正安静地停在他的指节上，翅膀微微合拢，像一片折叠起来的信纸。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=59</t>
+    <t>源类型=type:txt_pb; 层级=61</t>
   </si>
   <si>
     <t>68</t>
@@ -678,7 +690,7 @@
     <t>我希望你们能在这里结束我的生命。</t>
   </si>
   <si>
-    <t>源类型=type:txt_Gaiman; 层级=60</t>
+    <t>源类型=type:txt_Gaiman; 层级=62</t>
   </si>
   <si>
     <t>69</t>
@@ -687,7 +699,7 @@
     <t>众人的呼吸骤地冻在了原地，连培养罐内心脏规律的搏动也跟着顿住，仿佛被死亡掐住了血管。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=61</t>
+    <t>源类型=type:txt_pb; 层级=63</t>
   </si>
   <si>
     <t>70</t>
@@ -696,7 +708,7 @@
     <t>但他的话语没有停下，就像一盘正在播放遗言的录音带，按键里没有暂停的选项。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=62</t>
+    <t>源类型=type:txt_pb; 层级=64</t>
   </si>
   <si>
     <t>71</t>
@@ -705,7 +717,7 @@
     <t>因为只要我还活着，盖亚之心就始终存在于这颗大脑内，也就存在被人抢走的风险，这一点你们应该十分清楚。</t>
   </si>
   <si>
-    <t>源类型=type:txt_Gaiman; 层级=63</t>
+    <t>源类型=type:txt_Gaiman; 层级=65</t>
   </si>
   <si>
     <t>72</t>
@@ -714,7 +726,7 @@
     <t>他的视线越过你们，落在房间深处那三台静默的造梦设备上：</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=64</t>
+    <t>源类型=type:txt_pb; 层级=66</t>
   </si>
   <si>
     <t>73</t>
@@ -723,7 +735,7 @@
     <t>除此之外，我还需要你们需要把这颗携带异常代码的机械心脏带回现实——那是计划的一部分。两件事必须同时完成。因为一旦我消失，这片空间也会随之崩塌，你们必须在这之前通过这里的节点回到现实。</t>
   </si>
   <si>
-    <t>源类型=type:txt_Gaiman; 层级=65</t>
+    <t>源类型=type:txt_Gaiman; 层级=67</t>
   </si>
   <si>
     <t>74</t>
@@ -732,7 +744,7 @@
     <t>否则，你们会被卷进我的意识消亡时产生的余波里，再也醒不过来。</t>
   </si>
   <si>
-    <t>源类型=type:txt_Gaiman; 层级=66</t>
+    <t>源类型=type:txt_Gaiman; 层级=68</t>
   </si>
   <si>
     <t>75</t>
@@ -741,7 +753,7 @@
     <t>大卫的瞳孔在听到这句话时不露声色地收缩了一下，不是因为恐惧，反而像是下定了某种残酷的决心。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=67</t>
+    <t>源类型=type:txt_pb; 层级=69</t>
   </si>
   <si>
     <t>76</t>
@@ -750,7 +762,7 @@
     <t>索菲亚的声音从你身后传过来，比她平时的语调明显低了两度。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=68</t>
+    <t>源类型=type:txt_pb; 层级=70</t>
   </si>
   <si>
     <t>77</t>
@@ -759,7 +771,7 @@
     <t>……没有别的办法了吗？</t>
   </si>
   <si>
-    <t>源类型=type:txt_Sophia; 层级=69</t>
+    <t>源类型=type:txt_Sophia; 层级=71</t>
   </si>
   <si>
     <t>78</t>
@@ -768,7 +780,7 @@
     <t>盖曼看着她，脸上的肌肉在一秒内绷紧又放松——前半秒的紧绷里写着刚见面又要分开的不舍，后半秒的松弛则流露出传过火炬后的释然与解脱。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=70</t>
+    <t>源类型=type:txt_pb; 层级=72</t>
   </si>
   <si>
     <t>79</t>
@@ -777,7 +789,7 @@
     <t>那是在漫长的雪夜里走久了之后，终于看到了一扇像自己敞开的门时，发自内心的欣慰。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=71</t>
+    <t>源类型=type:txt_pb; 层级=73</t>
   </si>
   <si>
     <t>80</t>
@@ -786,7 +798,7 @@
     <t>别用那种眼神看着我，索菲亚。这是我早就渴望得到的解脱，只是为了等到一个契机，等到有人来将这颗‘炸弹’送出去，然后我才敢安心地迎来长眠。</t>
   </si>
   <si>
-    <t>源类型=type:txt_Gaiman; 层级=72</t>
+    <t>源类型=type:txt_Gaiman; 层级=74</t>
   </si>
   <si>
     <t>81</t>
@@ -795,7 +807,7 @@
     <t>索菲亚没有说话。她站在那里，眼眶里有泪光在晃动，但始终没有落下来。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=73</t>
+    <t>源类型=type:txt_pb; 层级=75</t>
   </si>
   <si>
     <t>82</t>
@@ -804,7 +816,7 @@
     <t>她努力克制着动作中的颤抖——伸出手，掌心朝上，伸向一直紧握着配枪握把的克拉克。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=74</t>
+    <t>源类型=type:txt_pb; 层级=76</t>
   </si>
   <si>
     <t>83</t>
@@ -813,7 +825,7 @@
     <t xml:space="preserve">……我来。 </t>
   </si>
   <si>
-    <t>源类型=type:txt_Sophia; 层级=75</t>
+    <t>源类型=type:txt_Sophia; 层级=77</t>
   </si>
   <si>
     <t>84</t>
@@ -822,7 +834,7 @@
     <t>她开口了，声音不高，却带着一种木已成舟的笃定。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=76</t>
+    <t>源类型=type:txt_pb; 层级=78</t>
   </si>
   <si>
     <t>85</t>
@@ -831,7 +843,7 @@
     <t>这是我这些年来一直想做的事情......一劳永逸地结束老师的痛苦，结束这对所有人来说都如噩梦般的一切。</t>
   </si>
   <si>
-    <t>源类型=type:txt_Sophia; 层级=77</t>
+    <t>源类型=type:txt_Sophia; 层级=79</t>
   </si>
   <si>
     <t>86</t>
@@ -840,7 +852,7 @@
     <t>她看着盖曼的眼睛，语气中泛起一丝令人心碎的柔软，像一朵被大风吹走的浮萍，经历了半生沉浮后，终于回到起点的归处。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=78</t>
+    <t>源类型=type:txt_pb; 层级=80</t>
   </si>
   <si>
     <t>87</t>
@@ -849,7 +861,7 @@
     <t>我会陪你留在这里的，老师。这也是我对自己的赎罪。</t>
   </si>
   <si>
-    <t>源类型=type:txt_Sophia; 层级=79</t>
+    <t>源类型=type:txt_Sophia; 层级=81</t>
   </si>
   <si>
     <t>88</t>
@@ -858,7 +870,7 @@
     <t>他慢慢地朝学生走近了一步，这一步耗尽了他身为师长的最后一点从容。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=80</t>
+    <t>源类型=type:txt_pb; 层级=82</t>
   </si>
   <si>
     <t>89</t>
@@ -867,7 +879,7 @@
     <t>而且……关于造梦设备的事，关于我的事，需要有人来记住。你是除了我之外唯一掌握这项技术全部操作细节的人，可以的话......用它们去做正确的事，要么就替我毁掉它们。</t>
   </si>
   <si>
-    <t>源类型=type:txt_Gaiman; 层级=81</t>
+    <t>源类型=type:txt_Gaiman; 层级=83</t>
   </si>
   <si>
     <t>90</t>
@@ -879,7 +891,7 @@
     <t>parallel(charfadeout(L,1);bgfade(sntzm_gy(s1)_90,1))</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=82</t>
+    <t>源类型=type:txt_pb; 层级=84</t>
   </si>
   <si>
     <t>91</t>
@@ -888,7 +900,7 @@
     <t>这是......我此生能教你的最后一堂课。</t>
   </si>
   <si>
-    <t>源类型=type:txt_Gaiman; 层级=83</t>
+    <t>源类型=type:txt_Gaiman; 层级=85</t>
   </si>
   <si>
     <t>92</t>
@@ -900,7 +912,7 @@
     <t>bgfade(sntzm_gy(s1)_92,1)</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=84</t>
+    <t>源类型=type:txt_pb; 层级=86</t>
   </si>
   <si>
     <t>93</t>
@@ -909,7 +921,7 @@
     <t>她接枪的动作很稳，没有了之前犹豫不决的颤抖。这份平稳并非来自麻木，更像是练习过很多次如何握紧一件她并不想握住的工具——</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=85</t>
+    <t>源类型=type:txt_pb; 层级=87</t>
   </si>
   <si>
     <t>94</t>
@@ -918,10 +930,55 @@
     <t>例如造梦设备的操纵杆，刺进病人皮肤的麻药注射器，还有很多很多她曾一度拒绝，却被命运强硬地塞进手里的东西，只是这一次，她不会再选择逃避了。</t>
   </si>
   <si>
-    <t>loadScript(盖亚之心（索菲亚线下）, 1)</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=86; gotomainline=盖亚之心（索菲亚线下）_1</t>
+    <r>
+      <t>loadScript(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>sntzm_gy(s2)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>, 1)</t>
+    </r>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=88; gotomainline=盖亚之心（索菲亚线下）_1</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <r>
+      <t>loadScript(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>sntzm_gy(ns2)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>, 24)</t>
+    </r>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=59; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"无视飞蛾（克拉克）","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]},{"sortnum":"2","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"无视飞蛾（克拉克）","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]},{"sortnum":"3","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"立刻离开","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}; gotomainline=盖亚之心（无索菲亚线下）_24</t>
   </si>
   <si>
     <t>36</t>
@@ -930,7 +987,7 @@
     <t>和从始至终都知道自己在做些什么的索菲亚不同，当他在B313房间里找到那盘记录着自己和阿兰过往恩怨的磁带，当他在亚波伦面前被提及那些自己不敢直面的往事时。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=32; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"端详飞蛾（大卫）","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}</t>
+    <t>源类型=type:txt_pb; 层级=33; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"端详飞蛾（大卫）","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}</t>
   </si>
   <si>
     <t>39</t>
@@ -945,7 +1002,34 @@
     <t>jump(41)</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=34; gotomainline=41</t>
+    <t>源类型=type:txt_pb; 层级=35; gotomainline=41</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <r>
+      <t>loadScript(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>sntzm_gy(ns2)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>, 12)</t>
+    </r>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=11; tag=盖亚之心（无索菲亚线下）_12; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"无视飞蛾（大卫）","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]},{"sortnum":"2","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"无视飞蛾（克拉克）","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"0","dowlist4":[]}]},{"sortnum":"3","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"立刻离开","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}; gotomainline=_</t>
   </si>
   <si>
     <t>项目</t>
@@ -957,13 +1041,13 @@
     <t>源 JSON</t>
   </si>
   <si>
-    <t>圣诺汀之梦_盖亚之心（索菲亚线上）.json</t>
+    <t>圣诺汀之梦_盖亚之心（索菲亚线上） (1).json</t>
   </si>
   <si>
     <t>转换时间</t>
   </si>
   <si>
-    <t>2026/9/9 11:25:34</t>
+    <t>2026/9/10 17:36:45</t>
   </si>
   <si>
     <t>输出节点数</t>
@@ -1515,7 +1599,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1677,6 +1761,11 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="34">
@@ -2130,12 +2219,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2670,7 +2762,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L93"/>
+  <dimension ref="A1:L97"/>
   <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -3101,7 +3193,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" ht="30" spans="1:12">
+    <row r="12" spans="1:12">
       <c r="A12" t="s">
         <v>48</v>
       </c>
@@ -3112,7 +3204,7 @@
         <v>14</v>
       </c>
       <c r="D12" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E12" t="s">
         <v>15</v>
@@ -3121,30 +3213,30 @@
         <v>15</v>
       </c>
       <c r="G12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" t="s">
+        <v>15</v>
+      </c>
+      <c r="J12" t="s">
+        <v>15</v>
+      </c>
+      <c r="K12" t="s">
+        <v>15</v>
+      </c>
+      <c r="L12" t="s">
         <v>49</v>
       </c>
-      <c r="H12" t="s">
-        <v>15</v>
-      </c>
-      <c r="I12" t="s">
-        <v>15</v>
-      </c>
-      <c r="J12" t="s">
-        <v>15</v>
-      </c>
-      <c r="K12" t="s">
-        <v>15</v>
-      </c>
-      <c r="L12" t="s">
+    </row>
+    <row r="13" ht="30" spans="1:12">
+      <c r="A13" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="13" ht="42" spans="1:12">
-      <c r="A13" t="s">
-        <v>51</v>
-      </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C13" t="s">
         <v>14</v>
@@ -3159,30 +3251,30 @@
         <v>15</v>
       </c>
       <c r="G13" t="s">
+        <v>51</v>
+      </c>
+      <c r="H13" t="s">
+        <v>15</v>
+      </c>
+      <c r="I13" t="s">
+        <v>15</v>
+      </c>
+      <c r="J13" t="s">
+        <v>15</v>
+      </c>
+      <c r="K13" t="s">
+        <v>15</v>
+      </c>
+      <c r="L13" t="s">
         <v>52</v>
       </c>
-      <c r="H13" t="s">
-        <v>15</v>
-      </c>
-      <c r="I13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J13" t="s">
-        <v>15</v>
-      </c>
-      <c r="K13" t="s">
-        <v>15</v>
-      </c>
-      <c r="L13" t="s">
+    </row>
+    <row r="14" ht="42" spans="1:12">
+      <c r="A14" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="14" ht="30" spans="1:12">
-      <c r="A14" t="s">
-        <v>54</v>
-      </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C14" t="s">
         <v>14</v>
@@ -3197,144 +3289,144 @@
         <v>15</v>
       </c>
       <c r="G14" t="s">
+        <v>54</v>
+      </c>
+      <c r="H14" t="s">
+        <v>15</v>
+      </c>
+      <c r="I14" t="s">
+        <v>15</v>
+      </c>
+      <c r="J14" t="s">
+        <v>15</v>
+      </c>
+      <c r="K14" t="s">
+        <v>15</v>
+      </c>
+      <c r="L14" t="s">
         <v>55</v>
       </c>
-      <c r="H14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I14" t="s">
-        <v>15</v>
-      </c>
-      <c r="J14" t="s">
-        <v>15</v>
-      </c>
-      <c r="K14" t="s">
+    </row>
+    <row r="15" ht="30" spans="1:12">
+      <c r="A15" t="s">
         <v>56</v>
       </c>
-      <c r="L14" t="s">
+      <c r="B15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" t="s">
+        <v>15</v>
+      </c>
+      <c r="F15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="A15" t="s">
+      <c r="H15" t="s">
+        <v>15</v>
+      </c>
+      <c r="I15" t="s">
+        <v>15</v>
+      </c>
+      <c r="J15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K15" t="s">
         <v>58</v>
       </c>
-      <c r="B15" t="s">
+      <c r="L15" t="s">
         <v>59</v>
       </c>
-      <c r="C15" t="s">
-        <v>14</v>
-      </c>
-      <c r="D15" t="s">
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" t="s">
         <v>60</v>
       </c>
-      <c r="E15" t="s">
-        <v>15</v>
-      </c>
-      <c r="F15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G15" t="s">
+      <c r="B16" t="s">
         <v>61</v>
       </c>
-      <c r="H15" t="s">
-        <v>15</v>
-      </c>
-      <c r="I15" t="s">
-        <v>15</v>
-      </c>
-      <c r="J15" t="s">
-        <v>15</v>
-      </c>
-      <c r="K15" t="s">
+      <c r="C16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" t="s">
+        <v>63</v>
+      </c>
+      <c r="H16" t="s">
+        <v>15</v>
+      </c>
+      <c r="I16" t="s">
+        <v>15</v>
+      </c>
+      <c r="J16" t="s">
+        <v>15</v>
+      </c>
+      <c r="K16" t="s">
         <v>22</v>
       </c>
-      <c r="L15" t="s">
+      <c r="L16" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" ht="54" spans="1:12">
+      <c r="A17" t="s">
+        <v>65</v>
+      </c>
+      <c r="B17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="16" ht="54" spans="1:12">
-      <c r="A16" t="s">
-        <v>63</v>
-      </c>
-      <c r="B16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16" t="s">
-        <v>14</v>
-      </c>
-      <c r="D16" t="s">
-        <v>60</v>
-      </c>
-      <c r="E16" t="s">
-        <v>15</v>
-      </c>
-      <c r="F16" t="s">
-        <v>15</v>
-      </c>
-      <c r="G16" t="s">
-        <v>64</v>
-      </c>
-      <c r="H16" t="s">
-        <v>15</v>
-      </c>
-      <c r="I16" t="s">
-        <v>15</v>
-      </c>
-      <c r="J16" t="s">
-        <v>15</v>
-      </c>
-      <c r="K16" t="s">
-        <v>56</v>
-      </c>
-      <c r="L16" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="17" ht="42" spans="1:12">
-      <c r="A17" t="s">
+      <c r="E17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" t="s">
         <v>66</v>
       </c>
-      <c r="B17" t="s">
+      <c r="H17" t="s">
+        <v>15</v>
+      </c>
+      <c r="I17" t="s">
+        <v>15</v>
+      </c>
+      <c r="J17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K17" t="s">
+        <v>58</v>
+      </c>
+      <c r="L17" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" ht="42" spans="1:12">
+      <c r="A18" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18" t="s">
         <v>19</v>
-      </c>
-      <c r="C17" t="s">
-        <v>14</v>
-      </c>
-      <c r="D17" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" t="s">
-        <v>15</v>
-      </c>
-      <c r="F17" t="s">
-        <v>15</v>
-      </c>
-      <c r="G17" t="s">
-        <v>67</v>
-      </c>
-      <c r="H17" t="s">
-        <v>15</v>
-      </c>
-      <c r="I17" t="s">
-        <v>15</v>
-      </c>
-      <c r="J17" t="s">
-        <v>15</v>
-      </c>
-      <c r="K17" t="s">
-        <v>22</v>
-      </c>
-      <c r="L17" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="18" ht="67.5" spans="1:12">
-      <c r="A18" t="s">
-        <v>69</v>
-      </c>
-      <c r="B18" t="s">
-        <v>13</v>
       </c>
       <c r="C18" t="s">
         <v>14</v>
@@ -3349,27 +3441,27 @@
         <v>15</v>
       </c>
       <c r="G18" t="s">
+        <v>69</v>
+      </c>
+      <c r="H18" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" t="s">
+        <v>15</v>
+      </c>
+      <c r="J18" t="s">
+        <v>15</v>
+      </c>
+      <c r="K18" t="s">
+        <v>22</v>
+      </c>
+      <c r="L18" t="s">
         <v>70</v>
       </c>
-      <c r="H18" t="s">
-        <v>15</v>
-      </c>
-      <c r="I18" t="s">
-        <v>15</v>
-      </c>
-      <c r="J18" t="s">
-        <v>15</v>
-      </c>
-      <c r="K18" t="s">
-        <v>56</v>
-      </c>
-      <c r="L18" t="s">
+    </row>
+    <row r="19" ht="67.5" spans="1:12">
+      <c r="A19" t="s">
         <v>71</v>
-      </c>
-    </row>
-    <row r="19" ht="27" spans="1:12">
-      <c r="A19" t="s">
-        <v>72</v>
       </c>
       <c r="B19" t="s">
         <v>13</v>
@@ -3378,7 +3470,7 @@
         <v>14</v>
       </c>
       <c r="D19" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E19" t="s">
         <v>15</v>
@@ -3387,27 +3479,27 @@
         <v>15</v>
       </c>
       <c r="G19" t="s">
+        <v>72</v>
+      </c>
+      <c r="H19" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" t="s">
+        <v>15</v>
+      </c>
+      <c r="J19" t="s">
+        <v>15</v>
+      </c>
+      <c r="K19" t="s">
+        <v>58</v>
+      </c>
+      <c r="L19" t="s">
         <v>73</v>
-      </c>
-      <c r="H19" t="s">
-        <v>15</v>
-      </c>
-      <c r="I19" t="s">
-        <v>15</v>
-      </c>
-      <c r="J19" t="s">
-        <v>15</v>
-      </c>
-      <c r="K19" t="s">
-        <v>15</v>
-      </c>
-      <c r="L19" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="20" ht="27" spans="1:12">
       <c r="A20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B20" t="s">
         <v>13</v>
@@ -3425,144 +3517,144 @@
         <v>15</v>
       </c>
       <c r="G20" t="s">
+        <v>75</v>
+      </c>
+      <c r="H20" t="s">
+        <v>15</v>
+      </c>
+      <c r="I20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J20" t="s">
+        <v>15</v>
+      </c>
+      <c r="K20" t="s">
+        <v>15</v>
+      </c>
+      <c r="L20" t="s">
         <v>76</v>
       </c>
-      <c r="H20" t="s">
-        <v>15</v>
-      </c>
-      <c r="I20" t="s">
-        <v>15</v>
-      </c>
-      <c r="J20" t="s">
-        <v>15</v>
-      </c>
-      <c r="K20" t="s">
-        <v>15</v>
-      </c>
-      <c r="L20" t="s">
+    </row>
+    <row r="21" ht="27" spans="1:12">
+      <c r="A21" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="21" ht="30" spans="1:12">
-      <c r="A21" t="s">
+      <c r="B21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F21" t="s">
+        <v>15</v>
+      </c>
+      <c r="G21" t="s">
         <v>78</v>
       </c>
-      <c r="B21" t="s">
+      <c r="H21" t="s">
+        <v>15</v>
+      </c>
+      <c r="I21" t="s">
+        <v>15</v>
+      </c>
+      <c r="J21" t="s">
+        <v>15</v>
+      </c>
+      <c r="K21" t="s">
+        <v>15</v>
+      </c>
+      <c r="L21" t="s">
         <v>79</v>
-      </c>
-      <c r="C21" t="s">
-        <v>14</v>
-      </c>
-      <c r="D21" t="s">
-        <v>80</v>
-      </c>
-      <c r="E21" t="s">
-        <v>15</v>
-      </c>
-      <c r="F21" t="s">
-        <v>15</v>
-      </c>
-      <c r="G21" t="s">
-        <v>81</v>
-      </c>
-      <c r="H21" t="s">
-        <v>15</v>
-      </c>
-      <c r="I21" t="s">
-        <v>15</v>
-      </c>
-      <c r="J21" t="s">
-        <v>15</v>
-      </c>
-      <c r="K21" t="s">
-        <v>22</v>
-      </c>
-      <c r="L21" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="22" ht="30" spans="1:12">
       <c r="A22" t="s">
+        <v>80</v>
+      </c>
+      <c r="B22" t="s">
+        <v>81</v>
+      </c>
+      <c r="C22" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" t="s">
+        <v>82</v>
+      </c>
+      <c r="E22" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" t="s">
         <v>83</v>
       </c>
-      <c r="B22" t="s">
-        <v>13</v>
-      </c>
-      <c r="C22" t="s">
-        <v>14</v>
-      </c>
-      <c r="D22" t="s">
-        <v>80</v>
-      </c>
-      <c r="E22" t="s">
-        <v>15</v>
-      </c>
-      <c r="F22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G22" t="s">
+      <c r="H22" t="s">
+        <v>15</v>
+      </c>
+      <c r="I22" t="s">
+        <v>15</v>
+      </c>
+      <c r="J22" t="s">
+        <v>15</v>
+      </c>
+      <c r="K22" t="s">
+        <v>22</v>
+      </c>
+      <c r="L22" t="s">
         <v>84</v>
-      </c>
-      <c r="H22" t="s">
-        <v>15</v>
-      </c>
-      <c r="I22" t="s">
-        <v>15</v>
-      </c>
-      <c r="J22" t="s">
-        <v>15</v>
-      </c>
-      <c r="K22" t="s">
-        <v>56</v>
-      </c>
-      <c r="L22" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="23" ht="30" spans="1:12">
       <c r="A23" t="s">
+        <v>85</v>
+      </c>
+      <c r="B23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" t="s">
+        <v>82</v>
+      </c>
+      <c r="E23" t="s">
+        <v>15</v>
+      </c>
+      <c r="F23" t="s">
+        <v>15</v>
+      </c>
+      <c r="G23" t="s">
         <v>86</v>
       </c>
-      <c r="B23" t="s">
+      <c r="H23" t="s">
+        <v>15</v>
+      </c>
+      <c r="I23" t="s">
+        <v>15</v>
+      </c>
+      <c r="J23" t="s">
+        <v>15</v>
+      </c>
+      <c r="K23" t="s">
+        <v>58</v>
+      </c>
+      <c r="L23" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="24" ht="30" spans="1:12">
+      <c r="A24" t="s">
+        <v>88</v>
+      </c>
+      <c r="B24" t="s">
         <v>19</v>
-      </c>
-      <c r="C23" t="s">
-        <v>14</v>
-      </c>
-      <c r="D23" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" t="s">
-        <v>15</v>
-      </c>
-      <c r="F23" t="s">
-        <v>15</v>
-      </c>
-      <c r="G23" t="s">
-        <v>87</v>
-      </c>
-      <c r="H23" t="s">
-        <v>15</v>
-      </c>
-      <c r="I23" t="s">
-        <v>15</v>
-      </c>
-      <c r="J23" t="s">
-        <v>15</v>
-      </c>
-      <c r="K23" t="s">
-        <v>22</v>
-      </c>
-      <c r="L23" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="24" ht="54" spans="1:12">
-      <c r="A24" t="s">
-        <v>89</v>
-      </c>
-      <c r="B24" t="s">
-        <v>13</v>
       </c>
       <c r="C24" t="s">
         <v>14</v>
@@ -3577,144 +3669,144 @@
         <v>15</v>
       </c>
       <c r="G24" t="s">
+        <v>89</v>
+      </c>
+      <c r="H24" t="s">
+        <v>15</v>
+      </c>
+      <c r="I24" t="s">
+        <v>15</v>
+      </c>
+      <c r="J24" t="s">
+        <v>15</v>
+      </c>
+      <c r="K24" t="s">
+        <v>22</v>
+      </c>
+      <c r="L24" t="s">
         <v>90</v>
       </c>
-      <c r="H24" t="s">
-        <v>15</v>
-      </c>
-      <c r="I24" t="s">
-        <v>15</v>
-      </c>
-      <c r="J24" t="s">
-        <v>15</v>
-      </c>
-      <c r="K24" t="s">
-        <v>56</v>
-      </c>
-      <c r="L24" t="s">
+    </row>
+    <row r="25" ht="54" spans="1:12">
+      <c r="A25" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="25" ht="57" spans="1:12">
-      <c r="A25" t="s">
+      <c r="B25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" t="s">
+        <v>15</v>
+      </c>
+      <c r="F25" t="s">
+        <v>15</v>
+      </c>
+      <c r="G25" t="s">
         <v>92</v>
       </c>
-      <c r="B25" t="s">
-        <v>79</v>
-      </c>
-      <c r="C25" t="s">
-        <v>14</v>
-      </c>
-      <c r="D25" t="s">
-        <v>80</v>
-      </c>
-      <c r="E25" t="s">
-        <v>15</v>
-      </c>
-      <c r="F25" t="s">
-        <v>15</v>
-      </c>
-      <c r="G25" t="s">
+      <c r="H25" t="s">
+        <v>15</v>
+      </c>
+      <c r="I25" t="s">
+        <v>15</v>
+      </c>
+      <c r="J25" t="s">
+        <v>15</v>
+      </c>
+      <c r="K25" t="s">
+        <v>58</v>
+      </c>
+      <c r="L25" t="s">
         <v>93</v>
       </c>
-      <c r="H25" t="s">
-        <v>15</v>
-      </c>
-      <c r="I25" t="s">
-        <v>15</v>
-      </c>
-      <c r="J25" t="s">
-        <v>15</v>
-      </c>
-      <c r="K25" t="s">
+    </row>
+    <row r="26" ht="57" spans="1:12">
+      <c r="A26" t="s">
+        <v>94</v>
+      </c>
+      <c r="B26" t="s">
+        <v>81</v>
+      </c>
+      <c r="C26" t="s">
+        <v>14</v>
+      </c>
+      <c r="D26" t="s">
+        <v>82</v>
+      </c>
+      <c r="E26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F26" t="s">
+        <v>15</v>
+      </c>
+      <c r="G26" t="s">
+        <v>95</v>
+      </c>
+      <c r="H26" t="s">
+        <v>15</v>
+      </c>
+      <c r="I26" t="s">
+        <v>15</v>
+      </c>
+      <c r="J26" t="s">
+        <v>15</v>
+      </c>
+      <c r="K26" t="s">
         <v>22</v>
       </c>
-      <c r="L25" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="26" ht="30" spans="1:12">
-      <c r="A26" t="s">
-        <v>95</v>
-      </c>
-      <c r="B26" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" t="s">
-        <v>14</v>
-      </c>
-      <c r="D26" t="s">
-        <v>80</v>
-      </c>
-      <c r="E26" t="s">
-        <v>15</v>
-      </c>
-      <c r="F26" t="s">
-        <v>15</v>
-      </c>
-      <c r="G26" t="s">
+      <c r="L26" t="s">
         <v>96</v>
-      </c>
-      <c r="H26" t="s">
-        <v>15</v>
-      </c>
-      <c r="I26" t="s">
-        <v>15</v>
-      </c>
-      <c r="J26" t="s">
-        <v>15</v>
-      </c>
-      <c r="K26" t="s">
-        <v>56</v>
-      </c>
-      <c r="L26" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="27" ht="30" spans="1:12">
       <c r="A27" t="s">
+        <v>97</v>
+      </c>
+      <c r="B27" t="s">
+        <v>13</v>
+      </c>
+      <c r="C27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D27" t="s">
+        <v>82</v>
+      </c>
+      <c r="E27" t="s">
+        <v>15</v>
+      </c>
+      <c r="F27" t="s">
+        <v>15</v>
+      </c>
+      <c r="G27" t="s">
         <v>98</v>
       </c>
-      <c r="B27" t="s">
+      <c r="H27" t="s">
+        <v>15</v>
+      </c>
+      <c r="I27" t="s">
+        <v>15</v>
+      </c>
+      <c r="J27" t="s">
+        <v>15</v>
+      </c>
+      <c r="K27" t="s">
+        <v>58</v>
+      </c>
+      <c r="L27" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="28" ht="30" spans="1:12">
+      <c r="A28" t="s">
+        <v>100</v>
+      </c>
+      <c r="B28" t="s">
         <v>19</v>
-      </c>
-      <c r="C27" t="s">
-        <v>14</v>
-      </c>
-      <c r="D27" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" t="s">
-        <v>15</v>
-      </c>
-      <c r="F27" t="s">
-        <v>15</v>
-      </c>
-      <c r="G27" t="s">
-        <v>99</v>
-      </c>
-      <c r="H27" t="s">
-        <v>15</v>
-      </c>
-      <c r="I27" t="s">
-        <v>15</v>
-      </c>
-      <c r="J27" t="s">
-        <v>15</v>
-      </c>
-      <c r="K27" t="s">
-        <v>22</v>
-      </c>
-      <c r="L27" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="28" ht="40.5" spans="1:12">
-      <c r="A28" t="s">
-        <v>101</v>
-      </c>
-      <c r="B28" t="s">
-        <v>13</v>
       </c>
       <c r="C28" t="s">
         <v>14</v>
@@ -3729,30 +3821,30 @@
         <v>15</v>
       </c>
       <c r="G28" t="s">
+        <v>101</v>
+      </c>
+      <c r="H28" t="s">
+        <v>15</v>
+      </c>
+      <c r="I28" t="s">
+        <v>15</v>
+      </c>
+      <c r="J28" t="s">
+        <v>15</v>
+      </c>
+      <c r="K28" t="s">
+        <v>22</v>
+      </c>
+      <c r="L28" t="s">
         <v>102</v>
       </c>
-      <c r="H28" t="s">
-        <v>15</v>
-      </c>
-      <c r="I28" t="s">
-        <v>15</v>
-      </c>
-      <c r="J28" t="s">
-        <v>15</v>
-      </c>
-      <c r="K28" t="s">
-        <v>15</v>
-      </c>
-      <c r="L28" t="s">
+    </row>
+    <row r="29" ht="40.5" spans="1:12">
+      <c r="A29" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="29" ht="54" spans="1:12">
-      <c r="A29" t="s">
-        <v>104</v>
-      </c>
       <c r="B29" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C29" t="s">
         <v>14</v>
@@ -3767,30 +3859,30 @@
         <v>15</v>
       </c>
       <c r="G29" t="s">
+        <v>104</v>
+      </c>
+      <c r="H29" t="s">
+        <v>15</v>
+      </c>
+      <c r="I29" t="s">
+        <v>15</v>
+      </c>
+      <c r="J29" t="s">
+        <v>15</v>
+      </c>
+      <c r="K29" t="s">
+        <v>15</v>
+      </c>
+      <c r="L29" t="s">
         <v>105</v>
       </c>
-      <c r="H29" t="s">
-        <v>15</v>
-      </c>
-      <c r="I29" t="s">
-        <v>15</v>
-      </c>
-      <c r="J29" t="s">
-        <v>15</v>
-      </c>
-      <c r="K29" t="s">
-        <v>15</v>
-      </c>
-      <c r="L29" t="s">
+    </row>
+    <row r="30" ht="54" spans="1:12">
+      <c r="A30" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="30" ht="30" spans="1:12">
-      <c r="A30" t="s">
-        <v>107</v>
-      </c>
       <c r="B30" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C30" t="s">
         <v>14</v>
@@ -3805,30 +3897,30 @@
         <v>15</v>
       </c>
       <c r="G30" t="s">
+        <v>107</v>
+      </c>
+      <c r="H30" t="s">
+        <v>15</v>
+      </c>
+      <c r="I30" t="s">
+        <v>15</v>
+      </c>
+      <c r="J30" t="s">
+        <v>15</v>
+      </c>
+      <c r="K30" t="s">
+        <v>15</v>
+      </c>
+      <c r="L30" t="s">
         <v>108</v>
-      </c>
-      <c r="H30" t="s">
-        <v>15</v>
-      </c>
-      <c r="I30" t="s">
-        <v>15</v>
-      </c>
-      <c r="J30" t="s">
-        <v>15</v>
-      </c>
-      <c r="K30" t="s">
-        <v>15</v>
-      </c>
-      <c r="L30" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="31" ht="30" spans="1:12">
       <c r="A31" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B31" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C31" t="s">
         <v>14</v>
@@ -3843,30 +3935,30 @@
         <v>15</v>
       </c>
       <c r="G31" t="s">
+        <v>110</v>
+      </c>
+      <c r="H31" t="s">
+        <v>15</v>
+      </c>
+      <c r="I31" t="s">
+        <v>15</v>
+      </c>
+      <c r="J31" t="s">
+        <v>15</v>
+      </c>
+      <c r="K31" t="s">
+        <v>15</v>
+      </c>
+      <c r="L31" t="s">
         <v>111</v>
-      </c>
-      <c r="H31" t="s">
-        <v>15</v>
-      </c>
-      <c r="I31" t="s">
-        <v>15</v>
-      </c>
-      <c r="J31" t="s">
-        <v>15</v>
-      </c>
-      <c r="K31" t="s">
-        <v>15</v>
-      </c>
-      <c r="L31" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="32" ht="30" spans="1:12">
       <c r="A32" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B32" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C32" t="s">
         <v>14</v>
@@ -3881,27 +3973,27 @@
         <v>15</v>
       </c>
       <c r="G32" t="s">
+        <v>113</v>
+      </c>
+      <c r="H32" t="s">
+        <v>15</v>
+      </c>
+      <c r="I32" t="s">
+        <v>15</v>
+      </c>
+      <c r="J32" t="s">
+        <v>15</v>
+      </c>
+      <c r="K32" t="s">
+        <v>15</v>
+      </c>
+      <c r="L32" t="s">
         <v>114</v>
       </c>
-      <c r="H32" t="s">
-        <v>15</v>
-      </c>
-      <c r="I32" t="s">
-        <v>15</v>
-      </c>
-      <c r="J32" t="s">
-        <v>15</v>
-      </c>
-      <c r="K32" t="s">
-        <v>56</v>
-      </c>
-      <c r="L32" t="s">
+    </row>
+    <row r="33" ht="30" spans="1:12">
+      <c r="A33" t="s">
         <v>115</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12">
-      <c r="A33" t="s">
-        <v>116</v>
       </c>
       <c r="B33" t="s">
         <v>13</v>
@@ -3910,7 +4002,7 @@
         <v>14</v>
       </c>
       <c r="D33" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E33" t="s">
         <v>15</v>
@@ -3919,7 +4011,7 @@
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>15</v>
+        <v>116</v>
       </c>
       <c r="H33" t="s">
         <v>15</v>
@@ -3931,13 +4023,13 @@
         <v>15</v>
       </c>
       <c r="K33" t="s">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="L33" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="34" ht="90" spans="1:12">
+    <row r="34" spans="1:12">
       <c r="A34" t="s">
         <v>118</v>
       </c>
@@ -3957,27 +4049,27 @@
         <v>15</v>
       </c>
       <c r="G34" t="s">
+        <v>15</v>
+      </c>
+      <c r="H34" t="s">
+        <v>15</v>
+      </c>
+      <c r="I34" t="s">
+        <v>15</v>
+      </c>
+      <c r="J34" t="s">
+        <v>15</v>
+      </c>
+      <c r="K34" t="s">
+        <v>15</v>
+      </c>
+      <c r="L34" t="s">
         <v>119</v>
       </c>
-      <c r="H34" t="s">
-        <v>15</v>
-      </c>
-      <c r="I34" t="s">
-        <v>15</v>
-      </c>
-      <c r="J34" t="s">
-        <v>15</v>
-      </c>
-      <c r="K34" t="s">
-        <v>15</v>
-      </c>
-      <c r="L34" t="s">
+    </row>
+    <row r="35" ht="90" spans="1:12">
+      <c r="A35" t="s">
         <v>120</v>
-      </c>
-    </row>
-    <row r="35" ht="67.5" spans="1:12">
-      <c r="A35" t="s">
-        <v>121</v>
       </c>
       <c r="B35" t="s">
         <v>13</v>
@@ -3995,27 +4087,27 @@
         <v>15</v>
       </c>
       <c r="G35" t="s">
+        <v>121</v>
+      </c>
+      <c r="H35" t="s">
+        <v>15</v>
+      </c>
+      <c r="I35" t="s">
+        <v>15</v>
+      </c>
+      <c r="J35" t="s">
+        <v>15</v>
+      </c>
+      <c r="K35" t="s">
+        <v>15</v>
+      </c>
+      <c r="L35" t="s">
         <v>122</v>
       </c>
-      <c r="H35" t="s">
-        <v>15</v>
-      </c>
-      <c r="I35" t="s">
-        <v>15</v>
-      </c>
-      <c r="J35" t="s">
-        <v>15</v>
-      </c>
-      <c r="K35" t="s">
-        <v>15</v>
-      </c>
-      <c r="L35" t="s">
+    </row>
+    <row r="36" ht="67.5" spans="1:12">
+      <c r="A36" t="s">
         <v>123</v>
-      </c>
-    </row>
-    <row r="36" ht="43.5" spans="1:12">
-      <c r="A36" t="s">
-        <v>124</v>
       </c>
       <c r="B36" t="s">
         <v>13</v>
@@ -4033,68 +4125,68 @@
         <v>15</v>
       </c>
       <c r="G36" t="s">
+        <v>124</v>
+      </c>
+      <c r="H36" t="s">
+        <v>15</v>
+      </c>
+      <c r="I36" t="s">
+        <v>15</v>
+      </c>
+      <c r="J36" t="s">
+        <v>15</v>
+      </c>
+      <c r="K36" t="s">
+        <v>15</v>
+      </c>
+      <c r="L36" t="s">
         <v>125</v>
       </c>
-      <c r="H36" t="s">
-        <v>15</v>
-      </c>
-      <c r="I36" t="s">
-        <v>15</v>
-      </c>
-      <c r="J36" t="s">
-        <v>15</v>
-      </c>
-      <c r="K36" t="s">
-        <v>15</v>
-      </c>
-      <c r="L36" t="s">
+    </row>
+    <row r="37" ht="43.5" spans="1:12">
+      <c r="A37" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="37" ht="54" spans="1:12">
-      <c r="A37" t="s">
+      <c r="B37" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37" t="s">
+        <v>14</v>
+      </c>
+      <c r="D37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E37" t="s">
+        <v>15</v>
+      </c>
+      <c r="F37" t="s">
+        <v>15</v>
+      </c>
+      <c r="G37" t="s">
         <v>127</v>
       </c>
-      <c r="B37" t="s">
-        <v>19</v>
-      </c>
-      <c r="C37" t="s">
-        <v>14</v>
-      </c>
-      <c r="D37" t="s">
-        <v>20</v>
-      </c>
-      <c r="E37" t="s">
-        <v>15</v>
-      </c>
-      <c r="F37" t="s">
-        <v>15</v>
-      </c>
-      <c r="G37" t="s">
+      <c r="H37" t="s">
+        <v>15</v>
+      </c>
+      <c r="I37" t="s">
+        <v>15</v>
+      </c>
+      <c r="J37" t="s">
+        <v>15</v>
+      </c>
+      <c r="K37" t="s">
+        <v>15</v>
+      </c>
+      <c r="L37" t="s">
         <v>128</v>
-      </c>
-      <c r="H37" t="s">
-        <v>15</v>
-      </c>
-      <c r="I37" t="s">
-        <v>15</v>
-      </c>
-      <c r="J37" t="s">
-        <v>15</v>
-      </c>
-      <c r="K37" t="s">
-        <v>22</v>
-      </c>
-      <c r="L37" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="38" ht="54" spans="1:12">
       <c r="A38" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B38" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C38" t="s">
         <v>14</v>
@@ -4109,30 +4201,30 @@
         <v>15</v>
       </c>
       <c r="G38" t="s">
+        <v>130</v>
+      </c>
+      <c r="H38" t="s">
+        <v>15</v>
+      </c>
+      <c r="I38" t="s">
+        <v>15</v>
+      </c>
+      <c r="J38" t="s">
+        <v>15</v>
+      </c>
+      <c r="K38" t="s">
+        <v>22</v>
+      </c>
+      <c r="L38" t="s">
         <v>131</v>
       </c>
-      <c r="H38" t="s">
-        <v>15</v>
-      </c>
-      <c r="I38" t="s">
-        <v>15</v>
-      </c>
-      <c r="J38" t="s">
-        <v>15</v>
-      </c>
-      <c r="K38" t="s">
-        <v>15</v>
-      </c>
-      <c r="L38" t="s">
+    </row>
+    <row r="39" ht="54" spans="1:12">
+      <c r="A39" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="39" ht="40.5" spans="1:12">
-      <c r="A39" t="s">
-        <v>133</v>
-      </c>
       <c r="B39" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C39" t="s">
         <v>14</v>
@@ -4147,30 +4239,30 @@
         <v>15</v>
       </c>
       <c r="G39" t="s">
+        <v>133</v>
+      </c>
+      <c r="H39" t="s">
+        <v>15</v>
+      </c>
+      <c r="I39" t="s">
+        <v>15</v>
+      </c>
+      <c r="J39" t="s">
+        <v>15</v>
+      </c>
+      <c r="K39" t="s">
+        <v>15</v>
+      </c>
+      <c r="L39" t="s">
         <v>134</v>
       </c>
-      <c r="H39" t="s">
-        <v>15</v>
-      </c>
-      <c r="I39" t="s">
-        <v>15</v>
-      </c>
-      <c r="J39" t="s">
-        <v>15</v>
-      </c>
-      <c r="K39" t="s">
-        <v>15</v>
-      </c>
-      <c r="L39" t="s">
+    </row>
+    <row r="40" ht="40.5" spans="1:12">
+      <c r="A40" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="40" ht="54" spans="1:12">
-      <c r="A40" t="s">
-        <v>136</v>
-      </c>
       <c r="B40" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C40" t="s">
         <v>14</v>
@@ -4185,27 +4277,27 @@
         <v>15</v>
       </c>
       <c r="G40" t="s">
+        <v>136</v>
+      </c>
+      <c r="H40" t="s">
+        <v>15</v>
+      </c>
+      <c r="I40" t="s">
+        <v>15</v>
+      </c>
+      <c r="J40" t="s">
+        <v>15</v>
+      </c>
+      <c r="K40" t="s">
+        <v>15</v>
+      </c>
+      <c r="L40" t="s">
         <v>137</v>
       </c>
-      <c r="H40" t="s">
-        <v>15</v>
-      </c>
-      <c r="I40" t="s">
-        <v>15</v>
-      </c>
-      <c r="J40" t="s">
-        <v>15</v>
-      </c>
-      <c r="K40" t="s">
-        <v>56</v>
-      </c>
-      <c r="L40" t="s">
+    </row>
+    <row r="41" ht="54" spans="1:12">
+      <c r="A41" t="s">
         <v>138</v>
-      </c>
-    </row>
-    <row r="41" ht="40.5" spans="1:12">
-      <c r="A41" t="s">
-        <v>139</v>
       </c>
       <c r="B41" t="s">
         <v>13</v>
@@ -4214,7 +4306,7 @@
         <v>14</v>
       </c>
       <c r="D41" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E41" t="s">
         <v>15</v>
@@ -4223,103 +4315,103 @@
         <v>15</v>
       </c>
       <c r="G41" t="s">
+        <v>139</v>
+      </c>
+      <c r="H41" t="s">
+        <v>15</v>
+      </c>
+      <c r="I41" t="s">
+        <v>15</v>
+      </c>
+      <c r="J41" t="s">
+        <v>15</v>
+      </c>
+      <c r="K41" t="s">
+        <v>58</v>
+      </c>
+      <c r="L41" t="s">
         <v>140</v>
       </c>
-      <c r="H41" t="s">
-        <v>15</v>
-      </c>
-      <c r="I41" t="s">
-        <v>15</v>
-      </c>
-      <c r="J41" t="s">
-        <v>15</v>
-      </c>
-      <c r="K41" t="s">
-        <v>15</v>
-      </c>
-      <c r="L41" t="s">
+    </row>
+    <row r="42" ht="40.5" spans="1:12">
+      <c r="A42" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="42" ht="27" spans="1:12">
-      <c r="A42" t="s">
+      <c r="B42" t="s">
+        <v>13</v>
+      </c>
+      <c r="C42" t="s">
+        <v>14</v>
+      </c>
+      <c r="D42" t="s">
+        <v>15</v>
+      </c>
+      <c r="E42" t="s">
+        <v>15</v>
+      </c>
+      <c r="F42" t="s">
+        <v>15</v>
+      </c>
+      <c r="G42" t="s">
         <v>142</v>
       </c>
-      <c r="B42" t="s">
+      <c r="H42" t="s">
+        <v>15</v>
+      </c>
+      <c r="I42" t="s">
+        <v>15</v>
+      </c>
+      <c r="J42" t="s">
+        <v>15</v>
+      </c>
+      <c r="K42" t="s">
+        <v>15</v>
+      </c>
+      <c r="L42" t="s">
         <v>143</v>
       </c>
-      <c r="C42" t="s">
-        <v>14</v>
-      </c>
-      <c r="D42" t="s">
+    </row>
+    <row r="43" ht="27" spans="1:12">
+      <c r="A43" t="s">
         <v>144</v>
       </c>
-      <c r="E42" t="s">
-        <v>15</v>
-      </c>
-      <c r="F42" t="s">
-        <v>15</v>
-      </c>
-      <c r="G42" t="s">
+      <c r="B43" t="s">
         <v>145</v>
       </c>
-      <c r="H42" t="s">
-        <v>15</v>
-      </c>
-      <c r="I42" t="s">
-        <v>15</v>
-      </c>
-      <c r="J42" t="s">
-        <v>15</v>
-      </c>
-      <c r="K42" t="s">
+      <c r="C43" t="s">
+        <v>14</v>
+      </c>
+      <c r="D43" t="s">
+        <v>146</v>
+      </c>
+      <c r="E43" t="s">
+        <v>15</v>
+      </c>
+      <c r="F43" t="s">
+        <v>15</v>
+      </c>
+      <c r="G43" t="s">
+        <v>147</v>
+      </c>
+      <c r="H43" t="s">
+        <v>15</v>
+      </c>
+      <c r="I43" t="s">
+        <v>15</v>
+      </c>
+      <c r="J43" t="s">
+        <v>15</v>
+      </c>
+      <c r="K43" t="s">
         <v>22</v>
       </c>
-      <c r="L42" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="43" ht="42" spans="1:12">
-      <c r="A43" t="s">
-        <v>147</v>
-      </c>
-      <c r="B43" t="s">
-        <v>13</v>
-      </c>
-      <c r="C43" t="s">
-        <v>14</v>
-      </c>
-      <c r="D43" t="s">
-        <v>144</v>
-      </c>
-      <c r="E43" t="s">
-        <v>15</v>
-      </c>
-      <c r="F43" t="s">
-        <v>15</v>
-      </c>
-      <c r="G43" t="s">
+      <c r="L43" t="s">
         <v>148</v>
       </c>
-      <c r="H43" t="s">
-        <v>15</v>
-      </c>
-      <c r="I43" t="s">
-        <v>15</v>
-      </c>
-      <c r="J43" t="s">
-        <v>15</v>
-      </c>
-      <c r="K43" t="s">
-        <v>56</v>
-      </c>
-      <c r="L43" t="s">
+    </row>
+    <row r="44" ht="42" spans="1:12">
+      <c r="A44" t="s">
         <v>149</v>
-      </c>
-    </row>
-    <row r="44" ht="54" spans="1:12">
-      <c r="A44" t="s">
-        <v>150</v>
       </c>
       <c r="B44" t="s">
         <v>13</v>
@@ -4328,7 +4420,7 @@
         <v>14</v>
       </c>
       <c r="D44" t="s">
-        <v>15</v>
+        <v>146</v>
       </c>
       <c r="E44" t="s">
         <v>15</v>
@@ -4337,27 +4429,27 @@
         <v>15</v>
       </c>
       <c r="G44" t="s">
+        <v>150</v>
+      </c>
+      <c r="H44" t="s">
+        <v>15</v>
+      </c>
+      <c r="I44" t="s">
+        <v>15</v>
+      </c>
+      <c r="J44" t="s">
+        <v>15</v>
+      </c>
+      <c r="K44" t="s">
+        <v>58</v>
+      </c>
+      <c r="L44" t="s">
         <v>151</v>
       </c>
-      <c r="H44" t="s">
-        <v>15</v>
-      </c>
-      <c r="I44" t="s">
-        <v>15</v>
-      </c>
-      <c r="J44" t="s">
-        <v>15</v>
-      </c>
-      <c r="K44" t="s">
-        <v>15</v>
-      </c>
-      <c r="L44" t="s">
+    </row>
+    <row r="45" ht="54" spans="1:12">
+      <c r="A45" t="s">
         <v>152</v>
-      </c>
-    </row>
-    <row r="45" ht="40.5" spans="1:12">
-      <c r="A45" t="s">
-        <v>153</v>
       </c>
       <c r="B45" t="s">
         <v>13</v>
@@ -4375,65 +4467,65 @@
         <v>15</v>
       </c>
       <c r="G45" t="s">
+        <v>153</v>
+      </c>
+      <c r="H45" t="s">
+        <v>15</v>
+      </c>
+      <c r="I45" t="s">
+        <v>15</v>
+      </c>
+      <c r="J45" t="s">
+        <v>15</v>
+      </c>
+      <c r="K45" t="s">
+        <v>15</v>
+      </c>
+      <c r="L45" t="s">
         <v>154</v>
       </c>
-      <c r="H45" t="s">
-        <v>15</v>
-      </c>
-      <c r="I45" t="s">
-        <v>15</v>
-      </c>
-      <c r="J45" t="s">
-        <v>15</v>
-      </c>
-      <c r="K45" t="s">
+    </row>
+    <row r="46" ht="40.5" spans="1:12">
+      <c r="A46" t="s">
         <v>155</v>
       </c>
-      <c r="L45" t="s">
+      <c r="B46" t="s">
+        <v>13</v>
+      </c>
+      <c r="C46" t="s">
+        <v>14</v>
+      </c>
+      <c r="D46" t="s">
+        <v>15</v>
+      </c>
+      <c r="E46" t="s">
+        <v>15</v>
+      </c>
+      <c r="F46" t="s">
+        <v>15</v>
+      </c>
+      <c r="G46" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="46" ht="42" spans="1:12">
-      <c r="A46" t="s">
+      <c r="H46" t="s">
+        <v>15</v>
+      </c>
+      <c r="I46" t="s">
+        <v>15</v>
+      </c>
+      <c r="J46" t="s">
+        <v>15</v>
+      </c>
+      <c r="K46" t="s">
         <v>157</v>
       </c>
-      <c r="B46" t="s">
-        <v>19</v>
-      </c>
-      <c r="C46" t="s">
-        <v>14</v>
-      </c>
-      <c r="D46" t="s">
-        <v>15</v>
-      </c>
-      <c r="E46" t="s">
-        <v>15</v>
-      </c>
-      <c r="F46" t="s">
-        <v>15</v>
-      </c>
-      <c r="G46" t="s">
+      <c r="L46" t="s">
         <v>158</v>
       </c>
-      <c r="H46" t="s">
-        <v>15</v>
-      </c>
-      <c r="I46" t="s">
-        <v>15</v>
-      </c>
-      <c r="J46" t="s">
-        <v>15</v>
-      </c>
-      <c r="K46" t="s">
-        <v>15</v>
-      </c>
-      <c r="L46" t="s">
+    </row>
+    <row r="47" ht="42" spans="1:12">
+      <c r="A47" t="s">
         <v>159</v>
-      </c>
-    </row>
-    <row r="47" ht="43.5" spans="1:12">
-      <c r="A47" t="s">
-        <v>160</v>
       </c>
       <c r="B47" t="s">
         <v>19</v>
@@ -4451,83 +4543,83 @@
         <v>15</v>
       </c>
       <c r="G47" t="s">
+        <v>160</v>
+      </c>
+      <c r="H47" t="s">
+        <v>15</v>
+      </c>
+      <c r="I47" t="s">
+        <v>15</v>
+      </c>
+      <c r="J47" t="s">
+        <v>15</v>
+      </c>
+      <c r="K47" t="s">
+        <v>15</v>
+      </c>
+      <c r="L47" t="s">
         <v>161</v>
       </c>
-      <c r="H47" t="s">
-        <v>15</v>
-      </c>
-      <c r="I47" t="s">
-        <v>15</v>
-      </c>
-      <c r="J47" t="s">
-        <v>15</v>
-      </c>
-      <c r="K47" t="s">
-        <v>15</v>
-      </c>
-      <c r="L47" t="s">
+    </row>
+    <row r="48" ht="43.5" spans="1:12">
+      <c r="A48" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="48" spans="1:12">
-      <c r="A48" t="s">
+      <c r="B48" t="s">
+        <v>19</v>
+      </c>
+      <c r="C48" t="s">
+        <v>14</v>
+      </c>
+      <c r="D48" t="s">
+        <v>15</v>
+      </c>
+      <c r="E48" t="s">
+        <v>15</v>
+      </c>
+      <c r="F48" t="s">
+        <v>15</v>
+      </c>
+      <c r="G48" t="s">
         <v>163</v>
       </c>
-      <c r="B48" t="s">
+      <c r="H48" t="s">
+        <v>15</v>
+      </c>
+      <c r="I48" t="s">
+        <v>15</v>
+      </c>
+      <c r="J48" t="s">
+        <v>15</v>
+      </c>
+      <c r="K48" t="s">
+        <v>15</v>
+      </c>
+      <c r="L48" t="s">
         <v>164</v>
-      </c>
-      <c r="C48" t="s">
-        <v>14</v>
-      </c>
-      <c r="D48" t="s">
-        <v>15</v>
-      </c>
-      <c r="E48" t="s">
-        <v>15</v>
-      </c>
-      <c r="F48" t="s">
-        <v>15</v>
-      </c>
-      <c r="G48" t="s">
-        <v>165</v>
-      </c>
-      <c r="H48" t="s">
-        <v>15</v>
-      </c>
-      <c r="I48" t="s">
-        <v>15</v>
-      </c>
-      <c r="J48" t="s">
-        <v>15</v>
-      </c>
-      <c r="K48" t="s">
-        <v>15</v>
-      </c>
-      <c r="L48" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="49" spans="1:12">
       <c r="A49" t="s">
+        <v>165</v>
+      </c>
+      <c r="B49" t="s">
+        <v>166</v>
+      </c>
+      <c r="C49" t="s">
+        <v>14</v>
+      </c>
+      <c r="D49" t="s">
+        <v>15</v>
+      </c>
+      <c r="E49" t="s">
+        <v>15</v>
+      </c>
+      <c r="F49" t="s">
+        <v>15</v>
+      </c>
+      <c r="G49" t="s">
         <v>167</v>
-      </c>
-      <c r="B49" t="s">
-        <v>59</v>
-      </c>
-      <c r="C49" t="s">
-        <v>14</v>
-      </c>
-      <c r="D49" t="s">
-        <v>15</v>
-      </c>
-      <c r="E49" t="s">
-        <v>15</v>
-      </c>
-      <c r="F49" t="s">
-        <v>15</v>
-      </c>
-      <c r="G49" t="s">
-        <v>165</v>
       </c>
       <c r="H49" t="s">
         <v>15</v>
@@ -4545,12 +4637,12 @@
         <v>168</v>
       </c>
     </row>
-    <row r="50" ht="28.5" spans="1:12">
+    <row r="50" spans="1:12">
       <c r="A50" t="s">
         <v>169</v>
       </c>
       <c r="B50" t="s">
-        <v>143</v>
+        <v>61</v>
       </c>
       <c r="C50" t="s">
         <v>14</v>
@@ -4565,106 +4657,106 @@
         <v>15</v>
       </c>
       <c r="G50" t="s">
+        <v>167</v>
+      </c>
+      <c r="H50" t="s">
+        <v>15</v>
+      </c>
+      <c r="I50" t="s">
+        <v>15</v>
+      </c>
+      <c r="J50" t="s">
+        <v>15</v>
+      </c>
+      <c r="K50" t="s">
+        <v>15</v>
+      </c>
+      <c r="L50" t="s">
         <v>170</v>
       </c>
-      <c r="H50" t="s">
-        <v>15</v>
-      </c>
-      <c r="I50" t="s">
-        <v>15</v>
-      </c>
-      <c r="J50" t="s">
-        <v>15</v>
-      </c>
-      <c r="K50" t="s">
-        <v>15</v>
-      </c>
-      <c r="L50" t="s">
+    </row>
+    <row r="51" ht="28.5" spans="1:12">
+      <c r="A51" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="51" ht="54" spans="1:12">
-      <c r="A51" t="s">
+      <c r="B51" t="s">
+        <v>145</v>
+      </c>
+      <c r="C51" t="s">
+        <v>14</v>
+      </c>
+      <c r="D51" t="s">
+        <v>15</v>
+      </c>
+      <c r="E51" t="s">
+        <v>15</v>
+      </c>
+      <c r="F51" t="s">
+        <v>15</v>
+      </c>
+      <c r="G51" t="s">
         <v>172</v>
       </c>
-      <c r="B51" t="s">
+      <c r="H51" t="s">
+        <v>15</v>
+      </c>
+      <c r="I51" t="s">
+        <v>15</v>
+      </c>
+      <c r="J51" t="s">
+        <v>15</v>
+      </c>
+      <c r="K51" t="s">
+        <v>15</v>
+      </c>
+      <c r="L51" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="52" ht="54" spans="1:12">
+      <c r="A52" t="s">
+        <v>174</v>
+      </c>
+      <c r="B52" t="s">
         <v>13</v>
       </c>
-      <c r="C51" t="s">
-        <v>14</v>
-      </c>
-      <c r="D51" t="s">
-        <v>15</v>
-      </c>
-      <c r="E51" t="s">
-        <v>15</v>
-      </c>
-      <c r="F51" t="s">
-        <v>15</v>
-      </c>
-      <c r="G51" t="s">
-        <v>173</v>
-      </c>
-      <c r="H51" t="s">
-        <v>15</v>
-      </c>
-      <c r="I51" t="s">
-        <v>15</v>
-      </c>
-      <c r="J51" t="s">
-        <v>15</v>
-      </c>
-      <c r="K51" t="s">
-        <v>174</v>
-      </c>
-      <c r="L51" t="s">
+      <c r="C52" t="s">
+        <v>14</v>
+      </c>
+      <c r="D52" t="s">
+        <v>15</v>
+      </c>
+      <c r="E52" t="s">
+        <v>15</v>
+      </c>
+      <c r="F52" t="s">
+        <v>15</v>
+      </c>
+      <c r="G52" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="52" ht="40.5" spans="1:12">
-      <c r="A52" t="s">
+      <c r="H52" t="s">
+        <v>15</v>
+      </c>
+      <c r="I52" t="s">
+        <v>15</v>
+      </c>
+      <c r="J52" t="s">
+        <v>15</v>
+      </c>
+      <c r="K52" t="s">
         <v>176</v>
       </c>
-      <c r="B52" t="s">
+      <c r="L52" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="53" ht="40.5" spans="1:12">
+      <c r="A53" t="s">
+        <v>178</v>
+      </c>
+      <c r="B53" t="s">
         <v>19</v>
-      </c>
-      <c r="C52" t="s">
-        <v>14</v>
-      </c>
-      <c r="D52" t="s">
-        <v>20</v>
-      </c>
-      <c r="E52" t="s">
-        <v>15</v>
-      </c>
-      <c r="F52" t="s">
-        <v>15</v>
-      </c>
-      <c r="G52" t="s">
-        <v>177</v>
-      </c>
-      <c r="H52" t="s">
-        <v>15</v>
-      </c>
-      <c r="I52" t="s">
-        <v>15</v>
-      </c>
-      <c r="J52" t="s">
-        <v>15</v>
-      </c>
-      <c r="K52" t="s">
-        <v>22</v>
-      </c>
-      <c r="L52" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="53" ht="55.5" spans="1:12">
-      <c r="A53" t="s">
-        <v>179</v>
-      </c>
-      <c r="B53" t="s">
-        <v>13</v>
       </c>
       <c r="C53" t="s">
         <v>14</v>
@@ -4679,27 +4771,27 @@
         <v>15</v>
       </c>
       <c r="G53" t="s">
+        <v>179</v>
+      </c>
+      <c r="H53" t="s">
+        <v>15</v>
+      </c>
+      <c r="I53" t="s">
+        <v>15</v>
+      </c>
+      <c r="J53" t="s">
+        <v>15</v>
+      </c>
+      <c r="K53" t="s">
+        <v>22</v>
+      </c>
+      <c r="L53" t="s">
         <v>180</v>
       </c>
-      <c r="H53" t="s">
-        <v>15</v>
-      </c>
-      <c r="I53" t="s">
-        <v>15</v>
-      </c>
-      <c r="J53" t="s">
-        <v>15</v>
-      </c>
-      <c r="K53" t="s">
-        <v>56</v>
-      </c>
-      <c r="L53" t="s">
+    </row>
+    <row r="54" ht="55.5" spans="1:12">
+      <c r="A54" t="s">
         <v>181</v>
-      </c>
-    </row>
-    <row r="54" ht="43.5" spans="1:12">
-      <c r="A54" t="s">
-        <v>182</v>
       </c>
       <c r="B54" t="s">
         <v>13</v>
@@ -4708,7 +4800,7 @@
         <v>14</v>
       </c>
       <c r="D54" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E54" t="s">
         <v>15</v>
@@ -4717,27 +4809,27 @@
         <v>15</v>
       </c>
       <c r="G54" t="s">
+        <v>182</v>
+      </c>
+      <c r="H54" t="s">
+        <v>15</v>
+      </c>
+      <c r="I54" t="s">
+        <v>15</v>
+      </c>
+      <c r="J54" t="s">
+        <v>15</v>
+      </c>
+      <c r="K54" t="s">
+        <v>58</v>
+      </c>
+      <c r="L54" t="s">
         <v>183</v>
       </c>
-      <c r="H54" t="s">
-        <v>15</v>
-      </c>
-      <c r="I54" t="s">
-        <v>15</v>
-      </c>
-      <c r="J54" t="s">
-        <v>15</v>
-      </c>
-      <c r="K54" t="s">
-        <v>15</v>
-      </c>
-      <c r="L54" t="s">
+    </row>
+    <row r="55" ht="43.5" spans="1:12">
+      <c r="A55" t="s">
         <v>184</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12">
-      <c r="A55" t="s">
-        <v>185</v>
       </c>
       <c r="B55" t="s">
         <v>13</v>
@@ -4755,7 +4847,7 @@
         <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>15</v>
+        <v>185</v>
       </c>
       <c r="H55" t="s">
         <v>15</v>
@@ -4773,7 +4865,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="56" ht="90" spans="1:12">
+    <row r="56" spans="1:12">
       <c r="A56" t="s">
         <v>187</v>
       </c>
@@ -4793,27 +4885,27 @@
         <v>15</v>
       </c>
       <c r="G56" t="s">
+        <v>15</v>
+      </c>
+      <c r="H56" t="s">
+        <v>15</v>
+      </c>
+      <c r="I56" t="s">
+        <v>15</v>
+      </c>
+      <c r="J56" t="s">
+        <v>15</v>
+      </c>
+      <c r="K56" t="s">
+        <v>15</v>
+      </c>
+      <c r="L56" t="s">
         <v>188</v>
       </c>
-      <c r="H56" t="s">
-        <v>15</v>
-      </c>
-      <c r="I56" t="s">
-        <v>15</v>
-      </c>
-      <c r="J56" t="s">
-        <v>15</v>
-      </c>
-      <c r="K56" t="s">
-        <v>15</v>
-      </c>
-      <c r="L56" t="s">
+    </row>
+    <row r="57" ht="90" spans="1:12">
+      <c r="A57" t="s">
         <v>189</v>
-      </c>
-    </row>
-    <row r="57" ht="54" spans="1:12">
-      <c r="A57" t="s">
-        <v>190</v>
       </c>
       <c r="B57" t="s">
         <v>13</v>
@@ -4831,27 +4923,27 @@
         <v>15</v>
       </c>
       <c r="G57" t="s">
+        <v>190</v>
+      </c>
+      <c r="H57" t="s">
+        <v>15</v>
+      </c>
+      <c r="I57" t="s">
+        <v>15</v>
+      </c>
+      <c r="J57" t="s">
+        <v>15</v>
+      </c>
+      <c r="K57" t="s">
+        <v>15</v>
+      </c>
+      <c r="L57" t="s">
         <v>191</v>
       </c>
-      <c r="H57" t="s">
-        <v>15</v>
-      </c>
-      <c r="I57" t="s">
-        <v>15</v>
-      </c>
-      <c r="J57" t="s">
-        <v>15</v>
-      </c>
-      <c r="K57" t="s">
+    </row>
+    <row r="58" ht="54" spans="1:12">
+      <c r="A58" t="s">
         <v>192</v>
-      </c>
-      <c r="L57" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="58" ht="90" spans="1:12">
-      <c r="A58" t="s">
-        <v>194</v>
       </c>
       <c r="B58" t="s">
         <v>13</v>
@@ -4869,27 +4961,27 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
+        <v>193</v>
+      </c>
+      <c r="H58" t="s">
+        <v>15</v>
+      </c>
+      <c r="I58" t="s">
+        <v>15</v>
+      </c>
+      <c r="J58" t="s">
+        <v>15</v>
+      </c>
+      <c r="K58" t="s">
+        <v>194</v>
+      </c>
+      <c r="L58" t="s">
         <v>195</v>
       </c>
-      <c r="H58" t="s">
-        <v>15</v>
-      </c>
-      <c r="I58" t="s">
-        <v>15</v>
-      </c>
-      <c r="J58" t="s">
-        <v>15</v>
-      </c>
-      <c r="K58" t="s">
-        <v>15</v>
-      </c>
-      <c r="L58" t="s">
+    </row>
+    <row r="59" ht="90" spans="1:12">
+      <c r="A59" t="s">
         <v>196</v>
-      </c>
-    </row>
-    <row r="59" ht="54" spans="1:12">
-      <c r="A59" t="s">
-        <v>197</v>
       </c>
       <c r="B59" t="s">
         <v>13</v>
@@ -4907,27 +4999,27 @@
         <v>15</v>
       </c>
       <c r="G59" t="s">
+        <v>197</v>
+      </c>
+      <c r="H59" t="s">
+        <v>15</v>
+      </c>
+      <c r="I59" t="s">
+        <v>15</v>
+      </c>
+      <c r="J59" t="s">
+        <v>15</v>
+      </c>
+      <c r="K59" t="s">
+        <v>15</v>
+      </c>
+      <c r="L59" t="s">
         <v>198</v>
       </c>
-      <c r="H59" t="s">
-        <v>15</v>
-      </c>
-      <c r="I59" t="s">
-        <v>15</v>
-      </c>
-      <c r="J59" t="s">
-        <v>15</v>
-      </c>
-      <c r="K59" t="s">
-        <v>15</v>
-      </c>
-      <c r="L59" t="s">
+    </row>
+    <row r="60" ht="54" spans="1:12">
+      <c r="A60" t="s">
         <v>199</v>
-      </c>
-    </row>
-    <row r="60" ht="40.5" spans="1:12">
-      <c r="A60" t="s">
-        <v>200</v>
       </c>
       <c r="B60" t="s">
         <v>13</v>
@@ -4945,27 +5037,27 @@
         <v>15</v>
       </c>
       <c r="G60" t="s">
+        <v>200</v>
+      </c>
+      <c r="H60" t="s">
+        <v>15</v>
+      </c>
+      <c r="I60" t="s">
+        <v>15</v>
+      </c>
+      <c r="J60" t="s">
+        <v>15</v>
+      </c>
+      <c r="K60" t="s">
+        <v>15</v>
+      </c>
+      <c r="L60" t="s">
         <v>201</v>
       </c>
-      <c r="H60" t="s">
-        <v>15</v>
-      </c>
-      <c r="I60" t="s">
-        <v>15</v>
-      </c>
-      <c r="J60" t="s">
-        <v>15</v>
-      </c>
-      <c r="K60" t="s">
-        <v>15</v>
-      </c>
-      <c r="L60" t="s">
+    </row>
+    <row r="61" ht="40.5" spans="1:12">
+      <c r="A61" t="s">
         <v>202</v>
-      </c>
-    </row>
-    <row r="61" ht="55.5" spans="1:12">
-      <c r="A61" t="s">
-        <v>203</v>
       </c>
       <c r="B61" t="s">
         <v>13</v>
@@ -4983,65 +5075,65 @@
         <v>15</v>
       </c>
       <c r="G61" t="s">
+        <v>203</v>
+      </c>
+      <c r="H61" t="s">
+        <v>15</v>
+      </c>
+      <c r="I61" t="s">
+        <v>15</v>
+      </c>
+      <c r="J61" t="s">
+        <v>15</v>
+      </c>
+      <c r="K61" t="s">
+        <v>15</v>
+      </c>
+      <c r="L61" t="s">
         <v>204</v>
       </c>
-      <c r="H61" t="s">
-        <v>15</v>
-      </c>
-      <c r="I61" t="s">
-        <v>15</v>
-      </c>
-      <c r="J61" t="s">
-        <v>15</v>
-      </c>
-      <c r="K61" t="s">
-        <v>15</v>
-      </c>
-      <c r="L61" t="s">
+    </row>
+    <row r="62" spans="1:12">
+      <c r="A62" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="62" ht="30" spans="1:12">
-      <c r="A62" t="s">
+      <c r="B62" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" t="s">
+        <v>14</v>
+      </c>
+      <c r="D62" t="s">
+        <v>15</v>
+      </c>
+      <c r="E62" t="s">
+        <v>15</v>
+      </c>
+      <c r="F62" t="s">
+        <v>15</v>
+      </c>
+      <c r="G62" t="s">
+        <v>15</v>
+      </c>
+      <c r="H62" t="s">
+        <v>15</v>
+      </c>
+      <c r="I62" t="s">
+        <v>15</v>
+      </c>
+      <c r="J62" t="s">
+        <v>15</v>
+      </c>
+      <c r="K62" t="s">
+        <v>15</v>
+      </c>
+      <c r="L62" t="s">
         <v>206</v>
       </c>
-      <c r="B62" t="s">
-        <v>19</v>
-      </c>
-      <c r="C62" t="s">
-        <v>14</v>
-      </c>
-      <c r="D62" t="s">
-        <v>20</v>
-      </c>
-      <c r="E62" t="s">
-        <v>15</v>
-      </c>
-      <c r="F62" t="s">
-        <v>15</v>
-      </c>
-      <c r="G62" t="s">
+    </row>
+    <row r="63" ht="55.5" spans="1:12">
+      <c r="A63" t="s">
         <v>207</v>
-      </c>
-      <c r="H62" t="s">
-        <v>15</v>
-      </c>
-      <c r="I62" t="s">
-        <v>15</v>
-      </c>
-      <c r="J62" t="s">
-        <v>15</v>
-      </c>
-      <c r="K62" t="s">
-        <v>22</v>
-      </c>
-      <c r="L62" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="63" ht="40.5" spans="1:12">
-      <c r="A63" t="s">
-        <v>209</v>
       </c>
       <c r="B63" t="s">
         <v>13</v>
@@ -5050,7 +5142,7 @@
         <v>14</v>
       </c>
       <c r="D63" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E63" t="s">
         <v>15</v>
@@ -5059,7 +5151,7 @@
         <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H63" t="s">
         <v>15</v>
@@ -5074,12 +5166,12 @@
         <v>15</v>
       </c>
       <c r="L63" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="64" ht="30" spans="1:12">
       <c r="A64" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B64" t="s">
         <v>19</v>
@@ -5097,27 +5189,27 @@
         <v>15</v>
       </c>
       <c r="G64" t="s">
+        <v>211</v>
+      </c>
+      <c r="H64" t="s">
+        <v>15</v>
+      </c>
+      <c r="I64" t="s">
+        <v>15</v>
+      </c>
+      <c r="J64" t="s">
+        <v>15</v>
+      </c>
+      <c r="K64" t="s">
+        <v>22</v>
+      </c>
+      <c r="L64" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="65" ht="40.5" spans="1:12">
+      <c r="A65" t="s">
         <v>213</v>
-      </c>
-      <c r="H64" t="s">
-        <v>15</v>
-      </c>
-      <c r="I64" t="s">
-        <v>15</v>
-      </c>
-      <c r="J64" t="s">
-        <v>15</v>
-      </c>
-      <c r="K64" t="s">
-        <v>15</v>
-      </c>
-      <c r="L64" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="65" ht="30" spans="1:12">
-      <c r="A65" t="s">
-        <v>215</v>
       </c>
       <c r="B65" t="s">
         <v>13</v>
@@ -5135,68 +5227,68 @@
         <v>15</v>
       </c>
       <c r="G65" t="s">
+        <v>214</v>
+      </c>
+      <c r="H65" t="s">
+        <v>15</v>
+      </c>
+      <c r="I65" t="s">
+        <v>15</v>
+      </c>
+      <c r="J65" t="s">
+        <v>15</v>
+      </c>
+      <c r="K65" t="s">
+        <v>15</v>
+      </c>
+      <c r="L65" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="66" ht="30" spans="1:12">
+      <c r="A66" t="s">
         <v>216</v>
       </c>
-      <c r="H65" t="s">
-        <v>15</v>
-      </c>
-      <c r="I65" t="s">
-        <v>15</v>
-      </c>
-      <c r="J65" t="s">
-        <v>15</v>
-      </c>
-      <c r="K65" t="s">
-        <v>56</v>
-      </c>
-      <c r="L65" t="s">
+      <c r="B66" t="s">
+        <v>19</v>
+      </c>
+      <c r="C66" t="s">
+        <v>14</v>
+      </c>
+      <c r="D66" t="s">
+        <v>20</v>
+      </c>
+      <c r="E66" t="s">
+        <v>15</v>
+      </c>
+      <c r="F66" t="s">
+        <v>15</v>
+      </c>
+      <c r="G66" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="66" ht="27" spans="1:12">
-      <c r="A66" t="s">
+      <c r="H66" t="s">
+        <v>15</v>
+      </c>
+      <c r="I66" t="s">
+        <v>15</v>
+      </c>
+      <c r="J66" t="s">
+        <v>15</v>
+      </c>
+      <c r="K66" t="s">
+        <v>15</v>
+      </c>
+      <c r="L66" t="s">
         <v>218</v>
       </c>
-      <c r="B66" t="s">
+    </row>
+    <row r="67" ht="30" spans="1:12">
+      <c r="A67" t="s">
+        <v>219</v>
+      </c>
+      <c r="B67" t="s">
         <v>13</v>
-      </c>
-      <c r="C66" t="s">
-        <v>14</v>
-      </c>
-      <c r="D66" t="s">
-        <v>15</v>
-      </c>
-      <c r="E66" t="s">
-        <v>15</v>
-      </c>
-      <c r="F66" t="s">
-        <v>15</v>
-      </c>
-      <c r="G66" t="s">
-        <v>219</v>
-      </c>
-      <c r="H66" t="s">
-        <v>15</v>
-      </c>
-      <c r="I66" t="s">
-        <v>15</v>
-      </c>
-      <c r="J66" t="s">
-        <v>15</v>
-      </c>
-      <c r="K66" t="s">
-        <v>15</v>
-      </c>
-      <c r="L66" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="67" ht="40.5" spans="1:12">
-      <c r="A67" t="s">
-        <v>221</v>
-      </c>
-      <c r="B67" t="s">
-        <v>19</v>
       </c>
       <c r="C67" t="s">
         <v>14</v>
@@ -5211,27 +5303,27 @@
         <v>15</v>
       </c>
       <c r="G67" t="s">
+        <v>220</v>
+      </c>
+      <c r="H67" t="s">
+        <v>15</v>
+      </c>
+      <c r="I67" t="s">
+        <v>15</v>
+      </c>
+      <c r="J67" t="s">
+        <v>15</v>
+      </c>
+      <c r="K67" t="s">
+        <v>58</v>
+      </c>
+      <c r="L67" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="68" ht="27" spans="1:12">
+      <c r="A68" t="s">
         <v>222</v>
-      </c>
-      <c r="H67" t="s">
-        <v>15</v>
-      </c>
-      <c r="I67" t="s">
-        <v>15</v>
-      </c>
-      <c r="J67" t="s">
-        <v>15</v>
-      </c>
-      <c r="K67" t="s">
-        <v>22</v>
-      </c>
-      <c r="L67" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="68" ht="30" spans="1:12">
-      <c r="A68" t="s">
-        <v>224</v>
       </c>
       <c r="B68" t="s">
         <v>13</v>
@@ -5240,7 +5332,7 @@
         <v>14</v>
       </c>
       <c r="D68" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E68" t="s">
         <v>15</v>
@@ -5249,27 +5341,27 @@
         <v>15</v>
       </c>
       <c r="G68" t="s">
+        <v>223</v>
+      </c>
+      <c r="H68" t="s">
+        <v>15</v>
+      </c>
+      <c r="I68" t="s">
+        <v>15</v>
+      </c>
+      <c r="J68" t="s">
+        <v>15</v>
+      </c>
+      <c r="K68" t="s">
+        <v>15</v>
+      </c>
+      <c r="L68" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="69" ht="40.5" spans="1:12">
+      <c r="A69" t="s">
         <v>225</v>
-      </c>
-      <c r="H68" t="s">
-        <v>15</v>
-      </c>
-      <c r="I68" t="s">
-        <v>15</v>
-      </c>
-      <c r="J68" t="s">
-        <v>15</v>
-      </c>
-      <c r="K68" t="s">
-        <v>15</v>
-      </c>
-      <c r="L68" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="69" ht="69" spans="1:12">
-      <c r="A69" t="s">
-        <v>227</v>
       </c>
       <c r="B69" t="s">
         <v>19</v>
@@ -5287,7 +5379,7 @@
         <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="H69" t="s">
         <v>15</v>
@@ -5299,18 +5391,18 @@
         <v>15</v>
       </c>
       <c r="K69" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="L69" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="70" ht="30" spans="1:12">
       <c r="A70" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B70" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C70" t="s">
         <v>14</v>
@@ -5325,30 +5417,30 @@
         <v>15</v>
       </c>
       <c r="G70" t="s">
+        <v>229</v>
+      </c>
+      <c r="H70" t="s">
+        <v>15</v>
+      </c>
+      <c r="I70" t="s">
+        <v>15</v>
+      </c>
+      <c r="J70" t="s">
+        <v>15</v>
+      </c>
+      <c r="K70" t="s">
+        <v>15</v>
+      </c>
+      <c r="L70" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="71" ht="69" spans="1:12">
+      <c r="A71" t="s">
         <v>231</v>
       </c>
-      <c r="H70" t="s">
-        <v>15</v>
-      </c>
-      <c r="I70" t="s">
-        <v>15</v>
-      </c>
-      <c r="J70" t="s">
-        <v>15</v>
-      </c>
-      <c r="K70" t="s">
-        <v>15</v>
-      </c>
-      <c r="L70" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="71" ht="40.5" spans="1:12">
-      <c r="A71" t="s">
-        <v>233</v>
-      </c>
       <c r="B71" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C71" t="s">
         <v>14</v>
@@ -5363,103 +5455,103 @@
         <v>15</v>
       </c>
       <c r="G71" t="s">
+        <v>232</v>
+      </c>
+      <c r="H71" t="s">
+        <v>15</v>
+      </c>
+      <c r="I71" t="s">
+        <v>15</v>
+      </c>
+      <c r="J71" t="s">
+        <v>15</v>
+      </c>
+      <c r="K71" t="s">
+        <v>15</v>
+      </c>
+      <c r="L71" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="72" ht="30" spans="1:12">
+      <c r="A72" t="s">
         <v>234</v>
       </c>
-      <c r="H71" t="s">
-        <v>15</v>
-      </c>
-      <c r="I71" t="s">
-        <v>15</v>
-      </c>
-      <c r="J71" t="s">
-        <v>15</v>
-      </c>
-      <c r="K71" t="s">
-        <v>56</v>
-      </c>
-      <c r="L71" t="s">
+      <c r="B72" t="s">
+        <v>19</v>
+      </c>
+      <c r="C72" t="s">
+        <v>14</v>
+      </c>
+      <c r="D72" t="s">
+        <v>20</v>
+      </c>
+      <c r="E72" t="s">
+        <v>15</v>
+      </c>
+      <c r="F72" t="s">
+        <v>15</v>
+      </c>
+      <c r="G72" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="72" ht="27" spans="1:12">
-      <c r="A72" t="s">
+      <c r="H72" t="s">
+        <v>15</v>
+      </c>
+      <c r="I72" t="s">
+        <v>15</v>
+      </c>
+      <c r="J72" t="s">
+        <v>15</v>
+      </c>
+      <c r="K72" t="s">
+        <v>15</v>
+      </c>
+      <c r="L72" t="s">
         <v>236</v>
       </c>
-      <c r="B72" t="s">
+    </row>
+    <row r="73" ht="40.5" spans="1:12">
+      <c r="A73" t="s">
+        <v>237</v>
+      </c>
+      <c r="B73" t="s">
         <v>13</v>
       </c>
-      <c r="C72" t="s">
-        <v>14</v>
-      </c>
-      <c r="D72" t="s">
-        <v>15</v>
-      </c>
-      <c r="E72" t="s">
-        <v>15</v>
-      </c>
-      <c r="F72" t="s">
-        <v>15</v>
-      </c>
-      <c r="G72" t="s">
-        <v>237</v>
-      </c>
-      <c r="H72" t="s">
-        <v>15</v>
-      </c>
-      <c r="I72" t="s">
-        <v>15</v>
-      </c>
-      <c r="J72" t="s">
-        <v>15</v>
-      </c>
-      <c r="K72" t="s">
-        <v>15</v>
-      </c>
-      <c r="L72" t="s">
+      <c r="C73" t="s">
+        <v>14</v>
+      </c>
+      <c r="D73" t="s">
+        <v>20</v>
+      </c>
+      <c r="E73" t="s">
+        <v>15</v>
+      </c>
+      <c r="F73" t="s">
+        <v>15</v>
+      </c>
+      <c r="G73" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="73" ht="30" spans="1:12">
-      <c r="A73" t="s">
+      <c r="H73" t="s">
+        <v>15</v>
+      </c>
+      <c r="I73" t="s">
+        <v>15</v>
+      </c>
+      <c r="J73" t="s">
+        <v>15</v>
+      </c>
+      <c r="K73" t="s">
+        <v>58</v>
+      </c>
+      <c r="L73" t="s">
         <v>239</v>
       </c>
-      <c r="B73" t="s">
-        <v>79</v>
-      </c>
-      <c r="C73" t="s">
-        <v>14</v>
-      </c>
-      <c r="D73" t="s">
-        <v>80</v>
-      </c>
-      <c r="E73" t="s">
-        <v>15</v>
-      </c>
-      <c r="F73" t="s">
-        <v>15</v>
-      </c>
-      <c r="G73" t="s">
+    </row>
+    <row r="74" ht="27" spans="1:12">
+      <c r="A74" t="s">
         <v>240</v>
-      </c>
-      <c r="H73" t="s">
-        <v>15</v>
-      </c>
-      <c r="I73" t="s">
-        <v>15</v>
-      </c>
-      <c r="J73" t="s">
-        <v>15</v>
-      </c>
-      <c r="K73" t="s">
-        <v>22</v>
-      </c>
-      <c r="L73" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="74" ht="42" spans="1:12">
-      <c r="A74" t="s">
-        <v>242</v>
       </c>
       <c r="B74" t="s">
         <v>13</v>
@@ -5468,7 +5560,7 @@
         <v>14</v>
       </c>
       <c r="D74" t="s">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="E74" t="s">
         <v>15</v>
@@ -5477,103 +5569,103 @@
         <v>15</v>
       </c>
       <c r="G74" t="s">
+        <v>241</v>
+      </c>
+      <c r="H74" t="s">
+        <v>15</v>
+      </c>
+      <c r="I74" t="s">
+        <v>15</v>
+      </c>
+      <c r="J74" t="s">
+        <v>15</v>
+      </c>
+      <c r="K74" t="s">
+        <v>15</v>
+      </c>
+      <c r="L74" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="75" ht="30" spans="1:12">
+      <c r="A75" t="s">
         <v>243</v>
       </c>
-      <c r="H74" t="s">
-        <v>15</v>
-      </c>
-      <c r="I74" t="s">
-        <v>15</v>
-      </c>
-      <c r="J74" t="s">
-        <v>15</v>
-      </c>
-      <c r="K74" t="s">
-        <v>56</v>
-      </c>
-      <c r="L74" t="s">
+      <c r="B75" t="s">
+        <v>81</v>
+      </c>
+      <c r="C75" t="s">
+        <v>14</v>
+      </c>
+      <c r="D75" t="s">
+        <v>82</v>
+      </c>
+      <c r="E75" t="s">
+        <v>15</v>
+      </c>
+      <c r="F75" t="s">
+        <v>15</v>
+      </c>
+      <c r="G75" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="75" ht="27" spans="1:12">
-      <c r="A75" t="s">
+      <c r="H75" t="s">
+        <v>15</v>
+      </c>
+      <c r="I75" t="s">
+        <v>15</v>
+      </c>
+      <c r="J75" t="s">
+        <v>15</v>
+      </c>
+      <c r="K75" t="s">
+        <v>22</v>
+      </c>
+      <c r="L75" t="s">
         <v>245</v>
-      </c>
-      <c r="B75" t="s">
-        <v>13</v>
-      </c>
-      <c r="C75" t="s">
-        <v>14</v>
-      </c>
-      <c r="D75" t="s">
-        <v>15</v>
-      </c>
-      <c r="E75" t="s">
-        <v>15</v>
-      </c>
-      <c r="F75" t="s">
-        <v>15</v>
-      </c>
-      <c r="G75" t="s">
-        <v>246</v>
-      </c>
-      <c r="H75" t="s">
-        <v>15</v>
-      </c>
-      <c r="I75" t="s">
-        <v>15</v>
-      </c>
-      <c r="J75" t="s">
-        <v>15</v>
-      </c>
-      <c r="K75" t="s">
-        <v>15</v>
-      </c>
-      <c r="L75" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="76" ht="42" spans="1:12">
       <c r="A76" t="s">
+        <v>246</v>
+      </c>
+      <c r="B76" t="s">
+        <v>13</v>
+      </c>
+      <c r="C76" t="s">
+        <v>14</v>
+      </c>
+      <c r="D76" t="s">
+        <v>82</v>
+      </c>
+      <c r="E76" t="s">
+        <v>15</v>
+      </c>
+      <c r="F76" t="s">
+        <v>15</v>
+      </c>
+      <c r="G76" t="s">
+        <v>247</v>
+      </c>
+      <c r="H76" t="s">
+        <v>15</v>
+      </c>
+      <c r="I76" t="s">
+        <v>15</v>
+      </c>
+      <c r="J76" t="s">
+        <v>15</v>
+      </c>
+      <c r="K76" t="s">
+        <v>58</v>
+      </c>
+      <c r="L76" t="s">
         <v>248</v>
       </c>
-      <c r="B76" t="s">
-        <v>19</v>
-      </c>
-      <c r="C76" t="s">
-        <v>14</v>
-      </c>
-      <c r="D76" t="s">
-        <v>20</v>
-      </c>
-      <c r="E76" t="s">
-        <v>15</v>
-      </c>
-      <c r="F76" t="s">
-        <v>15</v>
-      </c>
-      <c r="G76" t="s">
+    </row>
+    <row r="77" ht="27" spans="1:12">
+      <c r="A77" t="s">
         <v>249</v>
-      </c>
-      <c r="H76" t="s">
-        <v>15</v>
-      </c>
-      <c r="I76" t="s">
-        <v>15</v>
-      </c>
-      <c r="J76" t="s">
-        <v>15</v>
-      </c>
-      <c r="K76" t="s">
-        <v>22</v>
-      </c>
-      <c r="L76" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="77" ht="30" spans="1:12">
-      <c r="A77" t="s">
-        <v>251</v>
       </c>
       <c r="B77" t="s">
         <v>13</v>
@@ -5582,112 +5674,112 @@
         <v>14</v>
       </c>
       <c r="D77" t="s">
+        <v>15</v>
+      </c>
+      <c r="E77" t="s">
+        <v>15</v>
+      </c>
+      <c r="F77" t="s">
+        <v>15</v>
+      </c>
+      <c r="G77" t="s">
+        <v>250</v>
+      </c>
+      <c r="H77" t="s">
+        <v>15</v>
+      </c>
+      <c r="I77" t="s">
+        <v>15</v>
+      </c>
+      <c r="J77" t="s">
+        <v>15</v>
+      </c>
+      <c r="K77" t="s">
+        <v>15</v>
+      </c>
+      <c r="L77" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="78" ht="42" spans="1:12">
+      <c r="A78" t="s">
+        <v>252</v>
+      </c>
+      <c r="B78" t="s">
+        <v>19</v>
+      </c>
+      <c r="C78" t="s">
+        <v>14</v>
+      </c>
+      <c r="D78" t="s">
         <v>20</v>
       </c>
-      <c r="E77" t="s">
-        <v>15</v>
-      </c>
-      <c r="F77" t="s">
-        <v>15</v>
-      </c>
-      <c r="G77" t="s">
-        <v>252</v>
-      </c>
-      <c r="H77" t="s">
-        <v>15</v>
-      </c>
-      <c r="I77" t="s">
-        <v>15</v>
-      </c>
-      <c r="J77" t="s">
-        <v>15</v>
-      </c>
-      <c r="K77" t="s">
-        <v>56</v>
-      </c>
-      <c r="L77" t="s">
+      <c r="E78" t="s">
+        <v>15</v>
+      </c>
+      <c r="F78" t="s">
+        <v>15</v>
+      </c>
+      <c r="G78" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="78" ht="28.5" spans="1:12">
-      <c r="A78" t="s">
+      <c r="H78" t="s">
+        <v>15</v>
+      </c>
+      <c r="I78" t="s">
+        <v>15</v>
+      </c>
+      <c r="J78" t="s">
+        <v>15</v>
+      </c>
+      <c r="K78" t="s">
+        <v>22</v>
+      </c>
+      <c r="L78" t="s">
         <v>254</v>
-      </c>
-      <c r="B78" t="s">
-        <v>13</v>
-      </c>
-      <c r="C78" t="s">
-        <v>14</v>
-      </c>
-      <c r="D78" t="s">
-        <v>15</v>
-      </c>
-      <c r="E78" t="s">
-        <v>15</v>
-      </c>
-      <c r="F78" t="s">
-        <v>15</v>
-      </c>
-      <c r="G78" t="s">
-        <v>255</v>
-      </c>
-      <c r="H78" t="s">
-        <v>15</v>
-      </c>
-      <c r="I78" t="s">
-        <v>15</v>
-      </c>
-      <c r="J78" t="s">
-        <v>15</v>
-      </c>
-      <c r="K78" t="s">
-        <v>15</v>
-      </c>
-      <c r="L78" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="79" ht="30" spans="1:12">
       <c r="A79" t="s">
+        <v>255</v>
+      </c>
+      <c r="B79" t="s">
+        <v>13</v>
+      </c>
+      <c r="C79" t="s">
+        <v>14</v>
+      </c>
+      <c r="D79" t="s">
+        <v>20</v>
+      </c>
+      <c r="E79" t="s">
+        <v>15</v>
+      </c>
+      <c r="F79" t="s">
+        <v>15</v>
+      </c>
+      <c r="G79" t="s">
+        <v>256</v>
+      </c>
+      <c r="H79" t="s">
+        <v>15</v>
+      </c>
+      <c r="I79" t="s">
+        <v>15</v>
+      </c>
+      <c r="J79" t="s">
+        <v>15</v>
+      </c>
+      <c r="K79" t="s">
+        <v>58</v>
+      </c>
+      <c r="L79" t="s">
         <v>257</v>
       </c>
-      <c r="B79" t="s">
-        <v>79</v>
-      </c>
-      <c r="C79" t="s">
-        <v>14</v>
-      </c>
-      <c r="D79" t="s">
-        <v>80</v>
-      </c>
-      <c r="E79" t="s">
-        <v>15</v>
-      </c>
-      <c r="F79" t="s">
-        <v>15</v>
-      </c>
-      <c r="G79" t="s">
+    </row>
+    <row r="80" ht="28.5" spans="1:12">
+      <c r="A80" t="s">
         <v>258</v>
-      </c>
-      <c r="H79" t="s">
-        <v>15</v>
-      </c>
-      <c r="I79" t="s">
-        <v>15</v>
-      </c>
-      <c r="J79" t="s">
-        <v>15</v>
-      </c>
-      <c r="K79" t="s">
-        <v>22</v>
-      </c>
-      <c r="L79" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="80" ht="30" spans="1:12">
-      <c r="A80" t="s">
-        <v>260</v>
       </c>
       <c r="B80" t="s">
         <v>13</v>
@@ -5696,7 +5788,7 @@
         <v>14</v>
       </c>
       <c r="D80" t="s">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="E80" t="s">
         <v>15</v>
@@ -5705,65 +5797,65 @@
         <v>15</v>
       </c>
       <c r="G80" t="s">
+        <v>259</v>
+      </c>
+      <c r="H80" t="s">
+        <v>15</v>
+      </c>
+      <c r="I80" t="s">
+        <v>15</v>
+      </c>
+      <c r="J80" t="s">
+        <v>15</v>
+      </c>
+      <c r="K80" t="s">
+        <v>15</v>
+      </c>
+      <c r="L80" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="81" ht="30" spans="1:12">
+      <c r="A81" t="s">
         <v>261</v>
       </c>
-      <c r="H80" t="s">
-        <v>15</v>
-      </c>
-      <c r="I80" t="s">
-        <v>15</v>
-      </c>
-      <c r="J80" t="s">
-        <v>15</v>
-      </c>
-      <c r="K80" t="s">
-        <v>15</v>
-      </c>
-      <c r="L80" t="s">
+      <c r="B81" t="s">
+        <v>81</v>
+      </c>
+      <c r="C81" t="s">
+        <v>14</v>
+      </c>
+      <c r="D81" t="s">
+        <v>82</v>
+      </c>
+      <c r="E81" t="s">
+        <v>15</v>
+      </c>
+      <c r="F81" t="s">
+        <v>15</v>
+      </c>
+      <c r="G81" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="81" ht="42" spans="1:12">
-      <c r="A81" t="s">
+      <c r="H81" t="s">
+        <v>15</v>
+      </c>
+      <c r="I81" t="s">
+        <v>15</v>
+      </c>
+      <c r="J81" t="s">
+        <v>15</v>
+      </c>
+      <c r="K81" t="s">
+        <v>22</v>
+      </c>
+      <c r="L81" t="s">
         <v>263</v>
       </c>
-      <c r="B81" t="s">
-        <v>79</v>
-      </c>
-      <c r="C81" t="s">
-        <v>14</v>
-      </c>
-      <c r="D81" t="s">
-        <v>80</v>
-      </c>
-      <c r="E81" t="s">
-        <v>15</v>
-      </c>
-      <c r="F81" t="s">
-        <v>15</v>
-      </c>
-      <c r="G81" t="s">
+    </row>
+    <row r="82" ht="30" spans="1:12">
+      <c r="A82" t="s">
         <v>264</v>
-      </c>
-      <c r="H81" t="s">
-        <v>15</v>
-      </c>
-      <c r="I81" t="s">
-        <v>15</v>
-      </c>
-      <c r="J81" t="s">
-        <v>15</v>
-      </c>
-      <c r="K81" t="s">
-        <v>15</v>
-      </c>
-      <c r="L81" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="82" ht="40.5" spans="1:12">
-      <c r="A82" t="s">
-        <v>266</v>
       </c>
       <c r="B82" t="s">
         <v>13</v>
@@ -5772,7 +5864,7 @@
         <v>14</v>
       </c>
       <c r="D82" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E82" t="s">
         <v>15</v>
@@ -5781,65 +5873,65 @@
         <v>15</v>
       </c>
       <c r="G82" t="s">
+        <v>265</v>
+      </c>
+      <c r="H82" t="s">
+        <v>15</v>
+      </c>
+      <c r="I82" t="s">
+        <v>15</v>
+      </c>
+      <c r="J82" t="s">
+        <v>15</v>
+      </c>
+      <c r="K82" t="s">
+        <v>15</v>
+      </c>
+      <c r="L82" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="83" ht="42" spans="1:12">
+      <c r="A83" t="s">
         <v>267</v>
       </c>
-      <c r="H82" t="s">
-        <v>15</v>
-      </c>
-      <c r="I82" t="s">
-        <v>15</v>
-      </c>
-      <c r="J82" t="s">
-        <v>15</v>
-      </c>
-      <c r="K82" t="s">
-        <v>15</v>
-      </c>
-      <c r="L82" t="s">
+      <c r="B83" t="s">
+        <v>81</v>
+      </c>
+      <c r="C83" t="s">
+        <v>14</v>
+      </c>
+      <c r="D83" t="s">
+        <v>82</v>
+      </c>
+      <c r="E83" t="s">
+        <v>15</v>
+      </c>
+      <c r="F83" t="s">
+        <v>15</v>
+      </c>
+      <c r="G83" t="s">
         <v>268</v>
       </c>
-    </row>
-    <row r="83" ht="30" spans="1:12">
-      <c r="A83" t="s">
+      <c r="H83" t="s">
+        <v>15</v>
+      </c>
+      <c r="I83" t="s">
+        <v>15</v>
+      </c>
+      <c r="J83" t="s">
+        <v>15</v>
+      </c>
+      <c r="K83" t="s">
+        <v>15</v>
+      </c>
+      <c r="L83" t="s">
         <v>269</v>
       </c>
-      <c r="B83" t="s">
-        <v>79</v>
-      </c>
-      <c r="C83" t="s">
-        <v>14</v>
-      </c>
-      <c r="D83" t="s">
-        <v>80</v>
-      </c>
-      <c r="E83" t="s">
-        <v>15</v>
-      </c>
-      <c r="F83" t="s">
-        <v>15</v>
-      </c>
-      <c r="G83" t="s">
+    </row>
+    <row r="84" ht="40.5" spans="1:12">
+      <c r="A84" t="s">
         <v>270</v>
-      </c>
-      <c r="H83" t="s">
-        <v>15</v>
-      </c>
-      <c r="I83" t="s">
-        <v>15</v>
-      </c>
-      <c r="J83" t="s">
-        <v>15</v>
-      </c>
-      <c r="K83" t="s">
-        <v>15</v>
-      </c>
-      <c r="L83" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="84" ht="30" spans="1:12">
-      <c r="A84" t="s">
-        <v>272</v>
       </c>
       <c r="B84" t="s">
         <v>13</v>
@@ -5848,7 +5940,7 @@
         <v>14</v>
       </c>
       <c r="D84" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E84" t="s">
         <v>15</v>
@@ -5857,65 +5949,65 @@
         <v>15</v>
       </c>
       <c r="G84" t="s">
+        <v>271</v>
+      </c>
+      <c r="H84" t="s">
+        <v>15</v>
+      </c>
+      <c r="I84" t="s">
+        <v>15</v>
+      </c>
+      <c r="J84" t="s">
+        <v>15</v>
+      </c>
+      <c r="K84" t="s">
+        <v>15</v>
+      </c>
+      <c r="L84" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="85" ht="30" spans="1:12">
+      <c r="A85" t="s">
         <v>273</v>
       </c>
-      <c r="H84" t="s">
-        <v>15</v>
-      </c>
-      <c r="I84" t="s">
-        <v>15</v>
-      </c>
-      <c r="J84" t="s">
-        <v>15</v>
-      </c>
-      <c r="K84" t="s">
-        <v>56</v>
-      </c>
-      <c r="L84" t="s">
+      <c r="B85" t="s">
+        <v>81</v>
+      </c>
+      <c r="C85" t="s">
+        <v>14</v>
+      </c>
+      <c r="D85" t="s">
+        <v>82</v>
+      </c>
+      <c r="E85" t="s">
+        <v>15</v>
+      </c>
+      <c r="F85" t="s">
+        <v>15</v>
+      </c>
+      <c r="G85" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="85" ht="57" spans="1:12">
-      <c r="A85" t="s">
+      <c r="H85" t="s">
+        <v>15</v>
+      </c>
+      <c r="I85" t="s">
+        <v>15</v>
+      </c>
+      <c r="J85" t="s">
+        <v>15</v>
+      </c>
+      <c r="K85" t="s">
+        <v>15</v>
+      </c>
+      <c r="L85" t="s">
         <v>275</v>
       </c>
-      <c r="B85" t="s">
-        <v>19</v>
-      </c>
-      <c r="C85" t="s">
-        <v>14</v>
-      </c>
-      <c r="D85" t="s">
-        <v>20</v>
-      </c>
-      <c r="E85" t="s">
-        <v>15</v>
-      </c>
-      <c r="F85" t="s">
-        <v>15</v>
-      </c>
-      <c r="G85" t="s">
+    </row>
+    <row r="86" ht="30" spans="1:12">
+      <c r="A86" t="s">
         <v>276</v>
-      </c>
-      <c r="H85" t="s">
-        <v>15</v>
-      </c>
-      <c r="I85" t="s">
-        <v>15</v>
-      </c>
-      <c r="J85" t="s">
-        <v>15</v>
-      </c>
-      <c r="K85" t="s">
-        <v>22</v>
-      </c>
-      <c r="L85" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="86" ht="55.5" spans="1:12">
-      <c r="A86" t="s">
-        <v>278</v>
       </c>
       <c r="B86" t="s">
         <v>13</v>
@@ -5924,7 +6016,7 @@
         <v>14</v>
       </c>
       <c r="D86" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="E86" t="s">
         <v>15</v>
@@ -5933,27 +6025,27 @@
         <v>15</v>
       </c>
       <c r="G86" t="s">
+        <v>277</v>
+      </c>
+      <c r="H86" t="s">
+        <v>15</v>
+      </c>
+      <c r="I86" t="s">
+        <v>15</v>
+      </c>
+      <c r="J86" t="s">
+        <v>15</v>
+      </c>
+      <c r="K86" t="s">
+        <v>58</v>
+      </c>
+      <c r="L86" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="87" ht="57" spans="1:12">
+      <c r="A87" t="s">
         <v>279</v>
-      </c>
-      <c r="H86" t="s">
-        <v>15</v>
-      </c>
-      <c r="I86" t="s">
-        <v>15</v>
-      </c>
-      <c r="J86" t="s">
-        <v>15</v>
-      </c>
-      <c r="K86" t="s">
-        <v>280</v>
-      </c>
-      <c r="L86" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="87" spans="1:12">
-      <c r="A87" t="s">
-        <v>282</v>
       </c>
       <c r="B87" t="s">
         <v>19</v>
@@ -5962,7 +6054,7 @@
         <v>14</v>
       </c>
       <c r="D87" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E87" t="s">
         <v>15</v>
@@ -5971,7 +6063,7 @@
         <v>15</v>
       </c>
       <c r="G87" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="H87" t="s">
         <v>15</v>
@@ -5983,15 +6075,15 @@
         <v>15</v>
       </c>
       <c r="K87" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="L87" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="88" ht="40.5" spans="1:12">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="88" ht="55.5" spans="1:12">
       <c r="A88" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B88" t="s">
         <v>13</v>
@@ -6000,7 +6092,7 @@
         <v>14</v>
       </c>
       <c r="D88" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E88" t="s">
         <v>15</v>
@@ -6009,65 +6101,65 @@
         <v>15</v>
       </c>
       <c r="G88" t="s">
+        <v>283</v>
+      </c>
+      <c r="H88" t="s">
+        <v>15</v>
+      </c>
+      <c r="I88" t="s">
+        <v>15</v>
+      </c>
+      <c r="J88" t="s">
+        <v>15</v>
+      </c>
+      <c r="K88" t="s">
+        <v>284</v>
+      </c>
+      <c r="L88" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12">
+      <c r="A89" t="s">
         <v>286</v>
       </c>
-      <c r="H88" t="s">
-        <v>15</v>
-      </c>
-      <c r="I88" t="s">
-        <v>15</v>
-      </c>
-      <c r="J88" t="s">
-        <v>15</v>
-      </c>
-      <c r="K88" t="s">
+      <c r="B89" t="s">
+        <v>19</v>
+      </c>
+      <c r="C89" t="s">
+        <v>14</v>
+      </c>
+      <c r="D89" t="s">
+        <v>15</v>
+      </c>
+      <c r="E89" t="s">
+        <v>15</v>
+      </c>
+      <c r="F89" t="s">
+        <v>15</v>
+      </c>
+      <c r="G89" t="s">
         <v>287</v>
       </c>
-      <c r="L88" t="s">
+      <c r="H89" t="s">
+        <v>15</v>
+      </c>
+      <c r="I89" t="s">
+        <v>15</v>
+      </c>
+      <c r="J89" t="s">
+        <v>15</v>
+      </c>
+      <c r="K89" t="s">
+        <v>15</v>
+      </c>
+      <c r="L89" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="89" ht="42" spans="1:12">
-      <c r="A89" t="s">
+    <row r="90" ht="40.5" spans="1:12">
+      <c r="A90" t="s">
         <v>289</v>
-      </c>
-      <c r="B89" t="s">
-        <v>13</v>
-      </c>
-      <c r="C89" t="s">
-        <v>14</v>
-      </c>
-      <c r="D89" t="s">
-        <v>15</v>
-      </c>
-      <c r="E89" t="s">
-        <v>15</v>
-      </c>
-      <c r="F89" t="s">
-        <v>15</v>
-      </c>
-      <c r="G89" t="s">
-        <v>290</v>
-      </c>
-      <c r="H89" t="s">
-        <v>15</v>
-      </c>
-      <c r="I89" t="s">
-        <v>15</v>
-      </c>
-      <c r="J89" t="s">
-        <v>15</v>
-      </c>
-      <c r="K89" t="s">
-        <v>15</v>
-      </c>
-      <c r="L89" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="90" ht="54" spans="1:12">
-      <c r="A90" t="s">
-        <v>292</v>
       </c>
       <c r="B90" t="s">
         <v>13</v>
@@ -6085,27 +6177,27 @@
         <v>15</v>
       </c>
       <c r="G90" t="s">
+        <v>290</v>
+      </c>
+      <c r="H90" t="s">
+        <v>15</v>
+      </c>
+      <c r="I90" t="s">
+        <v>15</v>
+      </c>
+      <c r="J90" t="s">
+        <v>15</v>
+      </c>
+      <c r="K90" t="s">
+        <v>291</v>
+      </c>
+      <c r="L90" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="91" ht="42" spans="1:12">
+      <c r="A91" t="s">
         <v>293</v>
-      </c>
-      <c r="H90" t="s">
-        <v>15</v>
-      </c>
-      <c r="I90" t="s">
-        <v>15</v>
-      </c>
-      <c r="J90" t="s">
-        <v>15</v>
-      </c>
-      <c r="K90" t="s">
-        <v>294</v>
-      </c>
-      <c r="L90" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="91" ht="90" spans="1:12">
-      <c r="A91" t="s">
-        <v>296</v>
       </c>
       <c r="B91" t="s">
         <v>13</v>
@@ -6123,7 +6215,7 @@
         <v>15</v>
       </c>
       <c r="G91" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="H91" t="s">
         <v>15</v>
@@ -6138,12 +6230,12 @@
         <v>15</v>
       </c>
       <c r="L91" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="92" ht="67.5" spans="1:12">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="92" ht="54" spans="1:12">
       <c r="A92" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B92" t="s">
         <v>13</v>
@@ -6161,7 +6253,7 @@
         <v>15</v>
       </c>
       <c r="G92" t="s">
-        <v>122</v>
+        <v>297</v>
       </c>
       <c r="H92" t="s">
         <v>15</v>
@@ -6172,14 +6264,14 @@
       <c r="J92" t="s">
         <v>15</v>
       </c>
-      <c r="K92" t="s">
-        <v>15</v>
+      <c r="K92" s="2" t="s">
+        <v>298</v>
       </c>
       <c r="L92" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="93" ht="70.5" spans="1:12">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="93" ht="225" spans="1:12">
       <c r="A93" t="s">
         <v>300</v>
       </c>
@@ -6199,22 +6291,174 @@
         <v>15</v>
       </c>
       <c r="G93" t="s">
+        <v>208</v>
+      </c>
+      <c r="H93" t="s">
+        <v>15</v>
+      </c>
+      <c r="I93" t="s">
+        <v>15</v>
+      </c>
+      <c r="J93" t="s">
+        <v>15</v>
+      </c>
+      <c r="K93" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="H93" t="s">
-        <v>15</v>
-      </c>
-      <c r="I93" t="s">
-        <v>15</v>
-      </c>
-      <c r="J93" t="s">
-        <v>15</v>
-      </c>
-      <c r="K93" t="s">
+      <c r="L93" t="s">
         <v>302</v>
       </c>
-      <c r="L93" t="s">
+    </row>
+    <row r="94" ht="90" spans="1:12">
+      <c r="A94" t="s">
         <v>303</v>
+      </c>
+      <c r="B94" t="s">
+        <v>13</v>
+      </c>
+      <c r="C94" t="s">
+        <v>14</v>
+      </c>
+      <c r="D94" t="s">
+        <v>15</v>
+      </c>
+      <c r="E94" t="s">
+        <v>15</v>
+      </c>
+      <c r="F94" t="s">
+        <v>15</v>
+      </c>
+      <c r="G94" t="s">
+        <v>304</v>
+      </c>
+      <c r="H94" t="s">
+        <v>15</v>
+      </c>
+      <c r="I94" t="s">
+        <v>15</v>
+      </c>
+      <c r="J94" t="s">
+        <v>15</v>
+      </c>
+      <c r="K94" t="s">
+        <v>15</v>
+      </c>
+      <c r="L94" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="95" ht="67.5" spans="1:12">
+      <c r="A95" t="s">
+        <v>306</v>
+      </c>
+      <c r="B95" t="s">
+        <v>13</v>
+      </c>
+      <c r="C95" t="s">
+        <v>14</v>
+      </c>
+      <c r="D95" t="s">
+        <v>15</v>
+      </c>
+      <c r="E95" t="s">
+        <v>15</v>
+      </c>
+      <c r="F95" t="s">
+        <v>15</v>
+      </c>
+      <c r="G95" t="s">
+        <v>124</v>
+      </c>
+      <c r="H95" t="s">
+        <v>15</v>
+      </c>
+      <c r="I95" t="s">
+        <v>15</v>
+      </c>
+      <c r="J95" t="s">
+        <v>15</v>
+      </c>
+      <c r="K95" t="s">
+        <v>15</v>
+      </c>
+      <c r="L95" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="96" ht="70.5" spans="1:12">
+      <c r="A96" t="s">
+        <v>307</v>
+      </c>
+      <c r="B96" t="s">
+        <v>13</v>
+      </c>
+      <c r="C96" t="s">
+        <v>14</v>
+      </c>
+      <c r="D96" t="s">
+        <v>15</v>
+      </c>
+      <c r="E96" t="s">
+        <v>15</v>
+      </c>
+      <c r="F96" t="s">
+        <v>15</v>
+      </c>
+      <c r="G96" t="s">
+        <v>308</v>
+      </c>
+      <c r="H96" t="s">
+        <v>15</v>
+      </c>
+      <c r="I96" t="s">
+        <v>15</v>
+      </c>
+      <c r="J96" t="s">
+        <v>15</v>
+      </c>
+      <c r="K96" t="s">
+        <v>309</v>
+      </c>
+      <c r="L96" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="97" ht="225" spans="1:12">
+      <c r="A97" t="s">
+        <v>311</v>
+      </c>
+      <c r="B97" t="s">
+        <v>13</v>
+      </c>
+      <c r="C97" t="s">
+        <v>14</v>
+      </c>
+      <c r="D97" t="s">
+        <v>15</v>
+      </c>
+      <c r="E97" t="s">
+        <v>15</v>
+      </c>
+      <c r="F97" t="s">
+        <v>15</v>
+      </c>
+      <c r="G97" t="s">
+        <v>51</v>
+      </c>
+      <c r="H97" t="s">
+        <v>15</v>
+      </c>
+      <c r="I97" t="s">
+        <v>15</v>
+      </c>
+      <c r="J97" t="s">
+        <v>15</v>
+      </c>
+      <c r="K97" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="L97" t="s">
+        <v>313</v>
       </c>
     </row>
   </sheetData>
@@ -6235,122 +6479,122 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
     </row>
     <row r="2" ht="43.5" spans="1:2">
       <c r="A2" t="s">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="B2" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="B3" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="B4" t="s">
-        <v>285</v>
+        <v>311</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="B5" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="B8" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="B9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="B10" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="B11" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="B12" t="s">
-        <v>320</v>
+        <v>330</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="B13" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
     </row>
     <row r="14" ht="105" spans="1:2">
       <c r="A14" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="B14" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="B15" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
     </row>
   </sheetData>
@@ -6372,616 +6616,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="B2" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="C2" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="D2" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="E2" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="F2" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="B3" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="C3" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="D3" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="E3" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="F3" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="B4" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="C4" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="D4" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="E4" t="s">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="F4" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="B5" t="s">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="C5" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="D5" t="s">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="E5" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="F5" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="B6" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="C6" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="D6" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="E6" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="F6" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="B7" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="C7" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="D7" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="E7" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="F7" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="B8" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="C8" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="D8" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="E8" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="F8" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="B9" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="C9" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="D9" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="E9" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="F9" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="B10" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="C10" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="D10" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="E10" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="F10" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="B11" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="C11" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="D11" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="E11" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="F11" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="B12" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="C12" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="D12" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="E12" t="s">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="F12" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="B13" t="s">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="C13" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="D13" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="E13" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="F13" t="s">
-        <v>392</v>
+        <v>402</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="B14" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="C14" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="D14" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="E14" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="F14" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="B15" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="C15" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="D15" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="E15" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="F15" t="s">
-        <v>402</v>
+        <v>412</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="B16" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="C16" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="D16" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="E16" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="F16" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="B17" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="C17" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="D17" t="s">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="E17" t="s">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="F17" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="B18" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="C18" t="s">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="D18" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="E18" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="F18" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="B19" t="s">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="C19" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="D19" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="E19" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="F19" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="B20" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="C20" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="D20" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="E20" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="F20" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="B21" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="C21" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="D21" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="E21" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="F21" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="B22" t="s">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="C22" t="s">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="D22" t="s">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="E22" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="F22" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="B23" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="C23" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="D23" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="E23" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="F23" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="B24" t="s">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="C24" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="D24" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="E24" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="F24" t="s">
-        <v>446</v>
+        <v>456</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="B25" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="C25" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="D25" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="E25" t="s">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="F25" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="B26" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="C26" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="D26" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c r="E26" t="s">
-        <v>456</v>
+        <v>466</v>
       </c>
       <c r="F26" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="B27" t="s">
-        <v>458</v>
+        <v>468</v>
       </c>
       <c r="C27" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
       <c r="D27" t="s">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="E27" t="s">
-        <v>461</v>
+        <v>471</v>
       </c>
       <c r="F27" t="s">
-        <v>462</v>
+        <v>472</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="B28" t="s">
-        <v>463</v>
+        <v>473</v>
       </c>
       <c r="C28" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
       <c r="D28" t="s">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="E28" t="s">
-        <v>465</v>
+        <v>475</v>
       </c>
       <c r="F28" t="s">
-        <v>466</v>
+        <v>476</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="B29" t="s">
-        <v>467</v>
+        <v>477</v>
       </c>
       <c r="C29" t="s">
-        <v>468</v>
+        <v>478</v>
       </c>
       <c r="D29" t="s">
-        <v>469</v>
+        <v>479</v>
       </c>
       <c r="E29" t="s">
-        <v>470</v>
+        <v>480</v>
       </c>
       <c r="F29" t="s">
-        <v>471</v>
+        <v>481</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="B30" t="s">
-        <v>472</v>
+        <v>482</v>
       </c>
       <c r="C30" t="s">
-        <v>473</v>
+        <v>483</v>
       </c>
       <c r="D30" t="s">
-        <v>474</v>
+        <v>484</v>
       </c>
       <c r="E30" t="s">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="F30" t="s">
-        <v>476</v>
+        <v>486</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>477</v>
+        <v>487</v>
       </c>
       <c r="B31" t="s">
-        <v>478</v>
+        <v>488</v>
       </c>
       <c r="C31" t="s">
-        <v>479</v>
+        <v>489</v>
       </c>
       <c r="D31" t="s">
-        <v>480</v>
+        <v>490</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_gy(s1).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_gy(s1).xlsx
@@ -630,7 +630,7 @@
     <t>克拉克的枪口不自觉地放了下来，他看着那只安安静静停在手背的灰白色飞蛾，眉头渐渐舒展。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=55; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"无视飞蛾（大卫）","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}</t>
+    <t>源类型=type:txt_pb; 层级=55; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"大卫线","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}</t>
   </si>
   <si>
     <t>63</t>
@@ -931,6 +931,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>loadScript(</t>
     </r>
     <r>
@@ -958,6 +963,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>loadScript(</t>
     </r>
     <r>
@@ -1009,6 +1019,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>loadScript(</t>
     </r>
     <r>
